--- a/BVSimulationFiles/99.xlsx
+++ b/BVSimulationFiles/99.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\BVSimulationFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\BVSimulationFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD96031-0084-4E65-BC65-45FDC2F45660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B91A880-9206-4E73-90E3-6B54D2BBEB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="plot-data (2)" sheetId="1" r:id="rId1"/>
+    <sheet name="plot-data (1)" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -50,9 +50,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U72"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -446,7 +445,7 @@
         <v>5.1447368421052631E-2</v>
       </c>
       <c r="T1">
-        <v>5.4473684210526313E-2</v>
+        <v>5.447368421052632E-2</v>
       </c>
       <c r="U1">
         <v>5.7500000000000002E-2</v>
@@ -456,4615 +455,4680 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="1">
-        <v>3.299226708161972E-9</v>
+      <c r="B2">
+        <v>-1.1311651961044399E-2</v>
       </c>
       <c r="C2">
-        <v>3.1613766215204989E-9</v>
+        <v>-1.083902235998347E-2</v>
       </c>
       <c r="D2">
-        <v>3.029286262253945E-9</v>
+        <v>-1.038614042624543E-2</v>
       </c>
       <c r="E2">
-        <v>2.902714974297146E-9</v>
+        <v>-9.952181052042236E-3</v>
       </c>
       <c r="F2">
-        <v>2.7814321568076859E-9</v>
+        <v>-9.5363536046886872E-3</v>
       </c>
       <c r="G2">
-        <v>2.6652168440330982E-9</v>
+        <v>-9.1379004861449099E-3</v>
       </c>
       <c r="H2">
-        <v>2.5538573027322951E-9</v>
+        <v>-8.7560957527448198E-3</v>
       </c>
       <c r="I2">
-        <v>2.44715064641775E-9</v>
+        <v>-8.3902437925958469E-3</v>
       </c>
       <c r="J2">
-        <v>2.3449024657156251E-9</v>
+        <v>-8.039678058240244E-3</v>
       </c>
       <c r="K2">
-        <v>2.2469264741703862E-9</v>
+        <v>-7.7037598522690653E-3</v>
       </c>
       <c r="L2">
-        <v>2.1530441688486151E-9</v>
+        <v>-7.3818771636762516E-3</v>
       </c>
       <c r="M2">
-        <v>2.063084505123642E-9</v>
+        <v>-7.0734435528328216E-3</v>
       </c>
       <c r="N2">
-        <v>1.9768835850485208E-9</v>
+        <v>-6.7778970830496658E-3</v>
       </c>
       <c r="O2">
-        <v>1.8942843587495599E-9</v>
+        <v>-6.4946992967823761E-3</v>
       </c>
       <c r="P2">
-        <v>1.8151363382964019E-9</v>
+        <v>-6.2233342346128444E-3</v>
       </c>
       <c r="Q2">
-        <v>1.739295323527324E-9</v>
+        <v>-5.9633074952202773E-3</v>
       </c>
       <c r="R2">
-        <v>1.666623139330281E-9</v>
+        <v>-5.7141453346290678E-3</v>
       </c>
       <c r="S2">
-        <v>1.5969873839009871E-9</v>
+        <v>-5.475393803092329E-3</v>
       </c>
       <c r="T2">
-        <v>1.5302611875194309E-9</v>
+        <v>-5.2466179180386584E-3</v>
       </c>
       <c r="U2">
-        <v>1.466322981405322E-9</v>
+        <v>-5.0274008715752907E-3</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1.201945058955186E-2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>3.299226708161972E-9</v>
+        <v>8.4596456692912665E-3</v>
+      </c>
+      <c r="B3">
+        <v>1.6967477941566601E-2</v>
       </c>
       <c r="C3">
-        <v>3.1613766215204989E-9</v>
+        <v>1.6258533539975209E-2</v>
       </c>
       <c r="D3">
-        <v>3.029286262253945E-9</v>
+        <v>1.557921063936815E-2</v>
       </c>
       <c r="E3">
-        <v>2.902714974297146E-9</v>
+        <v>1.4928271578063351E-2</v>
       </c>
       <c r="F3">
-        <v>2.7814321568076859E-9</v>
+        <v>1.430453040703303E-2</v>
       </c>
       <c r="G3">
-        <v>2.6652168440330982E-9</v>
+        <v>1.370685072921737E-2</v>
       </c>
       <c r="H3">
-        <v>2.5538573027322951E-9</v>
+        <v>1.313414362911723E-2</v>
       </c>
       <c r="I3">
-        <v>2.44715064641775E-9</v>
+        <v>1.258536568889377E-2</v>
       </c>
       <c r="J3">
-        <v>2.3449024657156251E-9</v>
+        <v>1.2059517087360369E-2</v>
       </c>
       <c r="K3">
-        <v>2.2469264741703862E-9</v>
+        <v>1.15556397784036E-2</v>
       </c>
       <c r="L3">
-        <v>2.1530441688486151E-9</v>
+        <v>1.1072815745514379E-2</v>
       </c>
       <c r="M3">
-        <v>2.063084505123642E-9</v>
+        <v>1.061016532924923E-2</v>
       </c>
       <c r="N3">
-        <v>1.9768835850485208E-9</v>
+        <v>1.0166845624574501E-2</v>
       </c>
       <c r="O3">
-        <v>1.8942843587495599E-9</v>
+        <v>9.7420489451735641E-3</v>
       </c>
       <c r="P3">
-        <v>1.8151363382964019E-9</v>
+        <v>9.3350013519192671E-3</v>
       </c>
       <c r="Q3">
-        <v>1.739295323527324E-9</v>
+        <v>8.9449612428304168E-3</v>
       </c>
       <c r="R3">
-        <v>1.666623139330281E-9</v>
+        <v>8.5712180019436018E-3</v>
       </c>
       <c r="S3">
-        <v>1.5969873839009871E-9</v>
+        <v>8.2130907046384944E-3</v>
       </c>
       <c r="T3">
-        <v>1.5302611875194309E-9</v>
+        <v>7.869926877057988E-3</v>
       </c>
       <c r="U3">
-        <v>1.466322981405322E-9</v>
+        <v>7.5411013073629352E-3</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2.4038901179103719E-2</v>
-      </c>
-      <c r="B4" s="1">
-        <v>7.4232739088976917E-9</v>
+        <v>1.5979330708661438E-2</v>
+      </c>
+      <c r="B4">
+        <v>3.9590781863655493E-2</v>
       </c>
       <c r="C4">
-        <v>7.1131106367062466E-9</v>
+        <v>3.7936578259942233E-2</v>
       </c>
       <c r="D4">
-        <v>6.8159067752272622E-9</v>
+        <v>3.6351491491859088E-2</v>
       </c>
       <c r="E4">
-        <v>6.5311208473063744E-9</v>
+        <v>3.4832633682147909E-2</v>
       </c>
       <c r="F4">
-        <v>6.2582340000825028E-9</v>
+        <v>3.3377237616410482E-2</v>
       </c>
       <c r="G4">
-        <v>5.9967490596873042E-9</v>
+        <v>3.1982651701507263E-2</v>
       </c>
       <c r="H4">
-        <v>5.7461896254416949E-9</v>
+        <v>3.064633513460694E-2</v>
       </c>
       <c r="I4">
-        <v>5.5060992018991554E-9</v>
+        <v>2.9365853274085529E-2</v>
       </c>
       <c r="J4">
-        <v>5.2760403671544521E-9</v>
+        <v>2.8138873203840922E-2</v>
       </c>
       <c r="K4">
-        <v>5.0555939759025632E-9</v>
+        <v>2.6963159482941791E-2</v>
       </c>
       <c r="L4">
-        <v>4.8443583957958152E-9</v>
+        <v>2.5836570072866941E-2</v>
       </c>
       <c r="M4">
-        <v>4.6419487757079509E-9</v>
+        <v>2.4757052434914939E-2</v>
       </c>
       <c r="N4">
-        <v>4.4479963445720152E-9</v>
+        <v>2.3722639790673881E-2</v>
       </c>
       <c r="O4">
-        <v>4.262147739514558E-9</v>
+        <v>2.2731447538738372E-2</v>
       </c>
       <c r="P4">
-        <v>4.0840643620621018E-9</v>
+        <v>2.1781669821144999E-2</v>
       </c>
       <c r="Q4">
-        <v>3.9134217612469362E-9</v>
+        <v>2.087157623327102E-2</v>
       </c>
       <c r="R4">
-        <v>3.7499090424883468E-9</v>
+        <v>1.9999508671201781E-2</v>
       </c>
       <c r="S4">
-        <v>3.5932283011722571E-9</v>
+        <v>1.9163878310823199E-2</v>
       </c>
       <c r="T4">
-        <v>3.4430940798973749E-9</v>
+        <v>1.8363162713135341E-2</v>
       </c>
       <c r="U4">
-        <v>3.299232848398975E-9</v>
+        <v>1.7595903050513551E-2</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>3.1687643089997893E-2</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1.3196928937501099E-8</v>
+        <v>2.6318897637795241E-2</v>
+      </c>
+      <c r="B5">
+        <v>9.6149041668877486E-2</v>
       </c>
       <c r="C5">
-        <v>1.2645527667338191E-8</v>
+        <v>9.2131690059859592E-2</v>
       </c>
       <c r="D5">
-        <v>1.2117165345265201E-8</v>
+        <v>8.8282193623086258E-2</v>
       </c>
       <c r="E5">
-        <v>1.1610879345409059E-8</v>
+        <v>8.4593538942359089E-2</v>
       </c>
       <c r="F5">
-        <v>1.1125747262855079E-8</v>
+        <v>8.1059005639853923E-2</v>
       </c>
       <c r="G5">
-        <v>1.066088523311293E-8</v>
+        <v>7.7672154132231816E-2</v>
       </c>
       <c r="H5">
-        <v>1.021544632179963E-8</v>
+        <v>7.4426813898331043E-2</v>
       </c>
       <c r="I5">
-        <v>9.788618981605745E-9</v>
+        <v>7.1317072237064766E-2</v>
       </c>
       <c r="J5">
-        <v>9.379625573733371E-9</v>
+        <v>6.8337263495042141E-2</v>
       </c>
       <c r="K5">
-        <v>8.9877209511122572E-9</v>
+        <v>6.5481958744287125E-2</v>
       </c>
       <c r="L5">
-        <v>8.612191100812749E-9</v>
+        <v>6.274595589124822E-2</v>
       </c>
       <c r="M5">
-        <v>8.2523518431821761E-9</v>
+        <v>6.0124270199079052E-2</v>
       </c>
       <c r="N5">
-        <v>7.9075475853346321E-9</v>
+        <v>5.7612125205922217E-2</v>
       </c>
       <c r="O5">
-        <v>7.5771501267231157E-9</v>
+        <v>5.5204944022650249E-2</v>
       </c>
       <c r="P5">
-        <v>7.2605575146179234E-9</v>
+        <v>5.2898340994209231E-2</v>
       </c>
       <c r="Q5">
-        <v>6.9571929474060271E-9</v>
+        <v>5.0688113709372408E-2</v>
       </c>
       <c r="R5">
-        <v>6.6665037237134666E-9</v>
+        <v>4.857023534434713E-2</v>
       </c>
       <c r="S5">
-        <v>6.3879602354360051E-9</v>
+        <v>4.6540847326284843E-2</v>
       </c>
       <c r="T5">
-        <v>6.1210550028435723E-9</v>
+        <v>4.459625230332865E-2</v>
       </c>
       <c r="U5">
-        <v>5.865301750000489E-9</v>
+        <v>4.273290740839001E-2</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>3.8243706797281722E-2</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2.2269865936399489E-8</v>
+        <v>3.3838582677165267E-2</v>
+      </c>
+      <c r="B6">
+        <v>0.14139564951305539</v>
       </c>
       <c r="C6">
-        <v>2.133937427263113E-8</v>
+        <v>0.13548777949979379</v>
       </c>
       <c r="D6">
-        <v>2.044776091818062E-8</v>
+        <v>0.12982675532806831</v>
       </c>
       <c r="E6">
-        <v>1.9593401438360069E-8</v>
+        <v>0.1244022631505283</v>
       </c>
       <c r="F6">
-        <v>1.8774739271496179E-8</v>
+        <v>0.119204420058609</v>
       </c>
       <c r="G6">
-        <v>1.799028289302298E-8</v>
+        <v>0.11422375607681171</v>
       </c>
       <c r="H6">
-        <v>1.723860309806598E-8</v>
+        <v>0.1094511969093106</v>
       </c>
       <c r="I6">
-        <v>1.651833039756695E-8</v>
+        <v>0.1048780474074484</v>
       </c>
       <c r="J6">
-        <v>1.5828152523205101E-8</v>
+        <v>0.10049597572800339</v>
       </c>
       <c r="K6">
-        <v>1.5166812036569111E-8</v>
+        <v>9.6296998153363622E-2</v>
       </c>
       <c r="L6">
-        <v>1.453310403822403E-8</v>
+        <v>9.2273464545953449E-2</v>
       </c>
       <c r="M6">
-        <v>1.392587397249907E-8</v>
+        <v>8.8418044410410554E-2</v>
       </c>
       <c r="N6">
-        <v>1.334401552399715E-8</v>
+        <v>8.4723713538121095E-2</v>
       </c>
       <c r="O6">
-        <v>1.2786468601993431E-8</v>
+        <v>8.1183741209779961E-2</v>
       </c>
       <c r="P6">
-        <v>1.225221740905094E-8</v>
+        <v>7.7791677932660799E-2</v>
       </c>
       <c r="Q6">
-        <v>1.1740288590334269E-8</v>
+        <v>7.4541343690253697E-2</v>
       </c>
       <c r="R6">
-        <v>1.1249749460249719E-8</v>
+        <v>7.1426816682863575E-2</v>
       </c>
       <c r="S6">
-        <v>1.077970630318089E-8</v>
+        <v>6.8442422538654332E-2</v>
       </c>
       <c r="T6">
-        <v>1.032930274522382E-8</v>
+        <v>6.558272397548344E-2</v>
       </c>
       <c r="U6">
-        <v>9.8977181939553329E-9</v>
+        <v>6.2842510894691325E-2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>4.8077802358207439E-2</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3.2167535008458803E-8</v>
+        <v>4.1358267716535432E-2</v>
+      </c>
+      <c r="B7">
+        <v>0.214921387259844</v>
       </c>
       <c r="C7">
-        <v>3.0823493546564532E-8</v>
+        <v>0.2059414248396863</v>
       </c>
       <c r="D7">
-        <v>2.9535609556817749E-8</v>
+        <v>0.19733666809866349</v>
       </c>
       <c r="E7">
-        <v>2.8301536637141269E-8</v>
+        <v>0.18909143998880279</v>
       </c>
       <c r="F7">
-        <v>2.7119026424107069E-8</v>
+        <v>0.18119071848908541</v>
       </c>
       <c r="G7">
-        <v>2.5985924496632001E-8</v>
+        <v>0.17362010923675361</v>
       </c>
       <c r="H7">
-        <v>2.4900166450827639E-8</v>
+        <v>0.16636581930215191</v>
       </c>
       <c r="I7">
-        <v>2.3859774138852831E-8</v>
+        <v>0.15941463205932141</v>
       </c>
       <c r="J7">
-        <v>2.2862852064916539E-8</v>
+        <v>0.1527538831065649</v>
       </c>
       <c r="K7">
-        <v>2.1907583931864921E-8</v>
+        <v>0.14637143719311249</v>
       </c>
       <c r="L7">
-        <v>2.0992229332060719E-8</v>
+        <v>0.14025566610984899</v>
       </c>
       <c r="M7">
-        <v>2.011512057652619E-8</v>
+        <v>0.13439542750382391</v>
       </c>
       <c r="N7">
-        <v>1.927465965657243E-8</v>
+        <v>0.1287800445779439</v>
       </c>
       <c r="O7">
-        <v>1.8469315332379668E-8</v>
+        <v>0.1233992866388654</v>
       </c>
       <c r="P7">
-        <v>1.7697620343223989E-8</v>
+        <v>0.11824335045764429</v>
       </c>
       <c r="Q7">
-        <v>1.6958168734267871E-8</v>
+        <v>0.11330284240918551</v>
       </c>
       <c r="R7">
-        <v>1.6249613295044391E-8</v>
+        <v>0.1085687613579525</v>
       </c>
       <c r="S7">
-        <v>1.557066310496782E-8</v>
+        <v>0.1040324822587544</v>
       </c>
       <c r="T7">
-        <v>1.492008118139919E-8</v>
+        <v>9.9685740442734691E-2</v>
       </c>
       <c r="U7">
-        <v>1.429668222598169E-8</v>
+        <v>9.5520616559930674E-2</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>5.6819221094117377E-2</v>
-      </c>
-      <c r="B8" s="1">
-        <v>4.371477875110599E-8</v>
+        <v>4.7937992125984298E-2</v>
+      </c>
+      <c r="B8">
+        <v>0.29410295098715489</v>
       </c>
       <c r="C8">
-        <v>4.1888264064059827E-8</v>
+        <v>0.28181458135957071</v>
       </c>
       <c r="D8">
-        <v>4.013806580814537E-8</v>
+        <v>0.2700396510823817</v>
       </c>
       <c r="E8">
-        <v>3.8460995288685218E-8</v>
+        <v>0.25875670735309858</v>
       </c>
       <c r="F8">
-        <v>3.6853997042779223E-8</v>
+        <v>0.24794519372190629</v>
       </c>
       <c r="G8">
-        <v>3.5314143272541642E-8</v>
+        <v>0.2375854126397681</v>
       </c>
       <c r="H8">
-        <v>3.3838628510932163E-8</v>
+        <v>0.2276584895713657</v>
       </c>
       <c r="I8">
-        <v>3.2424764510461777E-8</v>
+        <v>0.21814633860749241</v>
       </c>
       <c r="J8">
-        <v>3.106997534546176E-8</v>
+        <v>0.2090316295142467</v>
       </c>
       <c r="K8">
-        <v>2.9771792718992171E-8</v>
+        <v>0.20029775615899609</v>
       </c>
       <c r="L8">
-        <v>2.852785146583972E-8</v>
+        <v>0.1919288062555829</v>
       </c>
       <c r="M8">
-        <v>2.7335885243411809E-8</v>
+        <v>0.18390953237365371</v>
       </c>
       <c r="N8">
-        <v>2.6193722402676019E-8</v>
+        <v>0.1762253241592916</v>
       </c>
       <c r="O8">
-        <v>2.5099282031622151E-8</v>
+        <v>0.1688621817163421</v>
       </c>
       <c r="P8">
-        <v>2.405057016403867E-8</v>
+        <v>0.1618066900999342</v>
       </c>
       <c r="Q8">
-        <v>2.3045676146695869E-8</v>
+        <v>0.15504599487572751</v>
       </c>
       <c r="R8">
-        <v>2.208276915831761E-8</v>
+        <v>0.14856777870035601</v>
       </c>
       <c r="S8">
-        <v>2.116009487399914E-8</v>
+        <v>0.14236023888040081</v>
       </c>
       <c r="T8">
-        <v>2.027597226899404E-8</v>
+        <v>0.13641206586900539</v>
       </c>
       <c r="U8">
-        <v>1.9428790556047111E-8</v>
+        <v>0.13071242266095781</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>6.3375286179995785E-2</v>
-      </c>
-      <c r="B9" s="1">
-        <v>5.8561392883460999E-8</v>
+        <v>5.7337598425196791E-2</v>
+      </c>
+      <c r="B9">
+        <v>0.41287529657812139</v>
       </c>
       <c r="C9">
-        <v>5.6114548881240907E-8</v>
+        <v>0.39562431613939741</v>
       </c>
       <c r="D9">
-        <v>5.3769940247348138E-8</v>
+        <v>0.37909412555795902</v>
       </c>
       <c r="E9">
-        <v>5.1523295327959387E-8</v>
+        <v>0.36325460839954232</v>
       </c>
       <c r="F9">
-        <v>4.9370520949817231E-8</v>
+        <v>0.34807690657113782</v>
       </c>
       <c r="G9">
-        <v>4.7307694962857858E-8</v>
+        <v>0.33353336774428988</v>
       </c>
       <c r="H9">
-        <v>4.5331059094426902E-8</v>
+        <v>0.31959749497518658</v>
       </c>
       <c r="I9">
-        <v>4.3437012102064318E-8</v>
+        <v>0.30624389842974897</v>
       </c>
       <c r="J9">
-        <v>4.1622103212383278E-8</v>
+        <v>0.2934482491257695</v>
       </c>
       <c r="K9">
-        <v>3.9883025834089442E-8</v>
+        <v>0.28118723460782152</v>
       </c>
       <c r="L9">
-        <v>3.821661153368622E-8</v>
+        <v>0.26943851647418382</v>
       </c>
       <c r="M9">
-        <v>3.6619824262890542E-8</v>
+        <v>0.25818068967839852</v>
       </c>
       <c r="N9">
-        <v>3.5089754827241698E-8</v>
+        <v>0.24739324353131331</v>
       </c>
       <c r="O9">
-        <v>3.3623615585825903E-8</v>
+        <v>0.23705652433255719</v>
       </c>
       <c r="P9">
-        <v>3.2218735372459833E-8</v>
+        <v>0.22715169956336931</v>
       </c>
       <c r="Q9">
-        <v>3.0872554629079933E-8</v>
+        <v>0.21766072357554059</v>
       </c>
       <c r="R9">
-        <v>2.9582620742471331E-8</v>
+        <v>0.2085663047139614</v>
       </c>
       <c r="S9">
-        <v>2.834658357583983E-8</v>
+        <v>0.1998518738128704</v>
       </c>
       <c r="T9">
-        <v>2.7162191187086341E-8</v>
+        <v>0.1915015540084114</v>
       </c>
       <c r="U9">
-        <v>2.6027285725982672E-8</v>
+        <v>0.1835001318124985</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>7.3209381740921509E-2</v>
-      </c>
-      <c r="B10" s="1">
-        <v>7.0933479223535152E-8</v>
+        <v>6.673720472440943E-2</v>
+      </c>
+      <c r="B10">
+        <v>0.53730346814961027</v>
       </c>
       <c r="C10">
-        <v>6.7969697973657668E-8</v>
+        <v>0.51485356209921607</v>
       </c>
       <c r="D10">
-        <v>6.5129751045644552E-8</v>
+        <v>0.49334167024665931</v>
       </c>
       <c r="E10">
-        <v>6.2408464326435898E-8</v>
+        <v>0.47272859997200739</v>
       </c>
       <c r="F10">
-        <v>5.9800879890580848E-8</v>
+        <v>0.45297679622271381</v>
       </c>
       <c r="G10">
-        <v>5.7302246967369143E-8</v>
+        <v>0.43405027309188432</v>
       </c>
       <c r="H10">
-        <v>5.4908013285378971E-8</v>
+        <v>0.41591454825537999</v>
       </c>
       <c r="I10">
-        <v>5.2613816778671682E-8</v>
+        <v>0.39853658014830368</v>
       </c>
       <c r="J10">
-        <v>5.0415477639522582E-8</v>
+        <v>0.38188470776641248</v>
       </c>
       <c r="K10">
-        <v>4.8308990703209191E-8</v>
+        <v>0.36592859298278152</v>
       </c>
       <c r="L10">
-        <v>4.62905181509821E-8</v>
+        <v>0.35063916527462291</v>
       </c>
       <c r="M10">
-        <v>4.4356382517924443E-8</v>
+        <v>0.3359885687595599</v>
       </c>
       <c r="N10">
-        <v>4.2503059992960812E-8</v>
+        <v>0.32195011144486002</v>
       </c>
       <c r="O10">
-        <v>4.0727173998808702E-8</v>
+        <v>0.30849821659716359</v>
       </c>
       <c r="P10">
-        <v>3.9025489040176143E-8</v>
+        <v>0.29560837614411078</v>
       </c>
       <c r="Q10">
-        <v>3.7394904808996947E-8</v>
+        <v>0.28325710602296378</v>
       </c>
       <c r="R10">
-        <v>3.5832450535964667E-8</v>
+        <v>0.27142190339488143</v>
       </c>
       <c r="S10">
-        <v>3.4335279578073499E-8</v>
+        <v>0.2600812056468863</v>
       </c>
       <c r="T10">
-        <v>3.2900664232305552E-8</v>
+        <v>0.2492143511068369</v>
       </c>
       <c r="U10">
-        <v>3.1525990766015633E-8</v>
+        <v>0.2388015413998269</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>7.9765445448205338E-2</v>
-      </c>
-      <c r="B11" s="1">
-        <v>8.7429668026478021E-8</v>
+        <v>7.6136811023622089E-2</v>
+      </c>
+      <c r="B11">
+        <v>0.63345250981848866</v>
       </c>
       <c r="C11">
-        <v>8.3776634034400647E-8</v>
+        <v>0.60698525215907662</v>
       </c>
       <c r="D11">
-        <v>8.0276233097537811E-8</v>
+        <v>0.58162386386974629</v>
       </c>
       <c r="E11">
-        <v>7.69220878184728E-8</v>
+        <v>0.55732213891436722</v>
       </c>
       <c r="F11">
-        <v>7.3708087263680111E-8</v>
+        <v>0.53403580186256838</v>
       </c>
       <c r="G11">
-        <v>7.0628375829985959E-8</v>
+        <v>0.51172242722411676</v>
       </c>
       <c r="H11">
-        <v>6.767734257621657E-8</v>
+        <v>0.49034136215371182</v>
       </c>
       <c r="I11">
-        <v>6.4849611000597284E-8</v>
+        <v>0.46985365238536908</v>
       </c>
       <c r="J11">
-        <v>6.2140029245277883E-8</v>
+        <v>0.4502219712614553</v>
       </c>
       <c r="K11">
-        <v>5.9543660710137902E-8</v>
+        <v>0.43141055172706921</v>
       </c>
       <c r="L11">
-        <v>5.7055775058770887E-8</v>
+        <v>0.41338512116587173</v>
       </c>
       <c r="M11">
-        <v>5.4671839600261677E-8</v>
+        <v>0.39611283895863952</v>
       </c>
       <c r="N11">
-        <v>5.2387511031054781E-8</v>
+        <v>0.3795622366507827</v>
       </c>
       <c r="O11">
-        <v>5.0198627521868687E-8</v>
+        <v>0.36370316061981439</v>
       </c>
       <c r="P11">
-        <v>4.8101201135238938E-8</v>
+        <v>0.34850671713832049</v>
       </c>
       <c r="Q11">
-        <v>4.6091410559875388E-8</v>
+        <v>0.33394521973233671</v>
       </c>
       <c r="R11">
-        <v>4.4165594148596932E-8</v>
+        <v>0.31999213873922899</v>
       </c>
       <c r="S11">
-        <v>4.2320243247158582E-8</v>
+        <v>0.30662205297317158</v>
       </c>
       <c r="T11">
-        <v>4.0551995801817322E-8</v>
+        <v>0.29381060341016602</v>
       </c>
       <c r="U11">
-        <v>3.8857630233990242E-8</v>
+        <v>0.28153444880821732</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>8.7414187359099504E-2</v>
-      </c>
-      <c r="B12" s="1">
-        <v>9.8976911769125194E-8</v>
+        <v>8.4596456692913408E-2</v>
+      </c>
+      <c r="B12">
+        <v>0.75222485540945527</v>
       </c>
       <c r="C12">
-        <v>9.4841404551895955E-8</v>
+        <v>0.72079498693890331</v>
       </c>
       <c r="D12">
-        <v>9.0878689348865435E-8</v>
+        <v>0.69067833834532366</v>
       </c>
       <c r="E12">
-        <v>8.7081546470016749E-8</v>
+        <v>0.66182003996081096</v>
       </c>
       <c r="F12">
-        <v>8.3443057882352246E-8</v>
+        <v>0.63416751471179988</v>
       </c>
       <c r="G12">
-        <v>7.99565946058956E-8</v>
+        <v>0.60767038232863868</v>
       </c>
       <c r="H12">
-        <v>7.661580463632108E-8</v>
+        <v>0.58228036755753254</v>
       </c>
       <c r="I12">
-        <v>7.341460137220623E-8</v>
+        <v>0.55795121220762578</v>
       </c>
       <c r="J12">
-        <v>7.0347152525823108E-8</v>
+        <v>0.53463859087297805</v>
       </c>
       <c r="K12">
-        <v>6.7407869497265149E-8</v>
+        <v>0.51230003017589465</v>
       </c>
       <c r="L12">
-        <v>6.4591397192549895E-8</v>
+        <v>0.49089483138447249</v>
       </c>
       <c r="M12">
-        <v>6.1892604267147299E-8</v>
+        <v>0.47038399626338429</v>
       </c>
       <c r="N12">
-        <v>5.9306573777158383E-8</v>
+        <v>0.45073015602280442</v>
       </c>
       <c r="O12">
-        <v>5.682859422111119E-8</v>
+        <v>0.43189750323602949</v>
       </c>
       <c r="P12">
-        <v>5.4454150956053632E-8</v>
+        <v>0.41385172660175562</v>
       </c>
       <c r="Q12">
-        <v>5.217891797230338E-8</v>
+        <v>0.39655994843214981</v>
       </c>
       <c r="R12">
-        <v>4.9998750011870151E-8</v>
+        <v>0.37999066475283427</v>
       </c>
       <c r="S12">
-        <v>4.7909675016189899E-8</v>
+        <v>0.36411368790564119</v>
       </c>
       <c r="T12">
-        <v>4.5907886889412169E-8</v>
+        <v>0.34890009154957202</v>
       </c>
       <c r="U12">
-        <v>4.3989738564055659E-8</v>
+        <v>0.334322157959758</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>9.2877574241367555E-2</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1.072250061705966E-7</v>
+        <v>9.3056102362204754E-2</v>
+      </c>
+      <c r="B13">
+        <v>0.84271807109781105</v>
       </c>
       <c r="C13">
-        <v>1.027448725822675E-7</v>
+        <v>0.80750716581877169</v>
       </c>
       <c r="D13">
-        <v>9.8451930374812077E-8</v>
+        <v>0.77376746175528766</v>
       </c>
       <c r="E13">
-        <v>9.4338358216035206E-8</v>
+        <v>0.74143748837714951</v>
       </c>
       <c r="F13">
-        <v>9.0396661568901884E-8</v>
+        <v>0.71045834354931003</v>
       </c>
       <c r="G13">
-        <v>8.6619659037204001E-8</v>
+        <v>0.68077358621779849</v>
       </c>
       <c r="H13">
-        <v>8.3000469281739883E-8</v>
+        <v>0.65232913357949174</v>
       </c>
       <c r="I13">
-        <v>7.9532498483169041E-8</v>
+        <v>0.62507316254839307</v>
       </c>
       <c r="J13">
-        <v>7.6209428328700765E-8</v>
+        <v>0.59895601533890053</v>
       </c>
       <c r="K13">
-        <v>7.3025204500729502E-8</v>
+        <v>0.57393010899404762</v>
       </c>
       <c r="L13">
-        <v>6.9974025646444295E-8</v>
+        <v>0.54994984869388308</v>
       </c>
       <c r="M13">
-        <v>6.7050332808315926E-8</v>
+        <v>0.52697154468604734</v>
       </c>
       <c r="N13">
-        <v>6.4248799296205364E-8</v>
+        <v>0.50495333268720211</v>
       </c>
       <c r="O13">
-        <v>6.1564320982641179E-8</v>
+        <v>0.48385509761028889</v>
       </c>
       <c r="P13">
-        <v>5.8992007003585029E-8</v>
+        <v>0.46363840047865867</v>
       </c>
       <c r="Q13">
-        <v>5.652717084774261E-8</v>
+        <v>0.4442664083939124</v>
       </c>
       <c r="R13">
-        <v>5.4165321818186283E-8</v>
+        <v>0.42570382742986718</v>
       </c>
       <c r="S13">
-        <v>5.1902156850732437E-8</v>
+        <v>0.40791683833038023</v>
       </c>
       <c r="T13">
-        <v>4.9733552674168058E-8</v>
+        <v>0.39087303489388159</v>
       </c>
       <c r="U13">
-        <v>4.765555829804296E-8</v>
+        <v>0.37454136493236062</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>0.10271166980229331</v>
+        <v>0.1024557086614174</v>
       </c>
       <c r="B14">
-        <v>1.162980536937611E-7</v>
+        <v>0.94452293874721005</v>
       </c>
       <c r="C14">
-        <v>1.114388250938414E-7</v>
+        <v>0.90505836705862241</v>
       </c>
       <c r="D14">
-        <v>1.067826274289746E-7</v>
+        <v>0.86724272559149607</v>
       </c>
       <c r="E14">
-        <v>1.023209775500886E-7</v>
+        <v>0.83100711784552916</v>
       </c>
       <c r="F14">
-        <v>9.8045746755664663E-8</v>
+        <v>0.7962855259915077</v>
       </c>
       <c r="G14">
-        <v>9.3949145982016726E-8</v>
+        <v>0.76301469059310223</v>
       </c>
       <c r="H14">
-        <v>9.0023711612358482E-8</v>
+        <v>0.73113399535419465</v>
       </c>
       <c r="I14">
-        <v>8.6262291878803967E-8</v>
+        <v>0.70058535668175526</v>
       </c>
       <c r="J14">
-        <v>8.2658033832526845E-8</v>
+        <v>0.67131311786306225</v>
       </c>
       <c r="K14">
-        <v>7.9204370858339915E-8</v>
+        <v>0.64326394766446882</v>
       </c>
       <c r="L14">
-        <v>7.5895010710947021E-8</v>
+        <v>0.61638674316696895</v>
       </c>
       <c r="M14">
-        <v>7.2723924051070858E-8</v>
+        <v>0.59063253666154236</v>
       </c>
       <c r="N14">
-        <v>6.9685333460570613E-8</v>
+        <v>0.56595440643464878</v>
       </c>
       <c r="O14">
-        <v>6.6773702916535869E-8</v>
+        <v>0.54230739128132999</v>
       </c>
       <c r="P14">
-        <v>6.3983727705179626E-8</v>
+        <v>0.51964840859017403</v>
       </c>
       <c r="Q14">
-        <v>6.1310324757154488E-8</v>
+        <v>0.49793617585089472</v>
       </c>
       <c r="R14">
-        <v>5.874862338668424E-8</v>
+        <v>0.47713113544152858</v>
       </c>
       <c r="S14">
-        <v>5.6293956417637602E-8</v>
+        <v>0.45719538255821079</v>
       </c>
       <c r="T14">
-        <v>5.3941851680377537E-8</v>
+        <v>0.43809259615622931</v>
       </c>
       <c r="U14">
-        <v>5.1688023863893823E-8</v>
+        <v>0.41978797277653801</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>0.1191018304490974</v>
+        <v>0.11561515748031501</v>
       </c>
       <c r="B15">
-        <v>1.2702001274191719E-7</v>
+        <v>0.99542537257190433</v>
       </c>
       <c r="C15">
-        <v>1.2171279341129129E-7</v>
+        <v>0.95383396767854267</v>
       </c>
       <c r="D15">
-        <v>1.166273232083451E-7</v>
+        <v>0.91398035750959539</v>
       </c>
       <c r="E15">
-        <v>1.1175433689029049E-7</v>
+        <v>0.87579193257971422</v>
       </c>
       <c r="F15">
-        <v>1.0708495633975859E-7</v>
+        <v>0.8391991172126021</v>
       </c>
       <c r="G15">
-        <v>1.026106743897141E-7</v>
+        <v>0.80413524278074988</v>
       </c>
       <c r="H15">
-        <v>9.8323339324206452E-8</v>
+        <v>0.77053642624154206</v>
       </c>
       <c r="I15">
-        <v>9.4215140026719633E-8</v>
+        <v>0.73834145374843241</v>
       </c>
       <c r="J15">
-        <v>9.027859174906056E-8</v>
+        <v>0.70749166912513939</v>
       </c>
       <c r="K15">
-        <v>8.6506522474860443E-8</v>
+        <v>0.67793086699967575</v>
       </c>
       <c r="L15">
-        <v>8.2892059852843316E-8</v>
+        <v>0.6496051904035085</v>
       </c>
       <c r="M15">
-        <v>7.9428618676056018E-8</v>
+        <v>0.6224630326492866</v>
       </c>
       <c r="N15">
-        <v>7.6109888884247686E-8</v>
+        <v>0.5964549433083689</v>
       </c>
       <c r="O15">
-        <v>7.292982406754053E-8</v>
+        <v>0.57153353811684748</v>
       </c>
       <c r="P15">
-        <v>6.9882630450446376E-8</v>
+        <v>0.54765341264592882</v>
       </c>
       <c r="Q15">
-        <v>6.6962756336158873E-8</v>
+        <v>0.52477105957938297</v>
       </c>
       <c r="R15">
-        <v>6.4164881991890508E-8</v>
+        <v>0.50284478944735655</v>
       </c>
       <c r="S15">
-        <v>6.1483909956825448E-8</v>
+        <v>0.48183465467212361</v>
       </c>
       <c r="T15">
-        <v>5.8914955755031078E-8</v>
+        <v>0.46170237678740073</v>
       </c>
       <c r="U15">
-        <v>5.6453338996407649E-8</v>
+        <v>0.44241127669862429</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>0.13330663606727541</v>
+        <v>0.12501476377952761</v>
       </c>
       <c r="B16">
-        <v>1.3444392769155789E-7</v>
+        <v>1.0463278063966071</v>
       </c>
       <c r="C16">
-        <v>1.2882651830442721E-7</v>
+        <v>1.002609568298471</v>
       </c>
       <c r="D16">
-        <v>1.234438185748054E-7</v>
+        <v>0.96071798942770281</v>
       </c>
       <c r="E16">
-        <v>1.182860217359906E-7</v>
+        <v>0.92057674731390737</v>
       </c>
       <c r="F16">
-        <v>1.1334373077294691E-7</v>
+        <v>0.88211270843370404</v>
       </c>
       <c r="G16">
-        <v>1.086079413018368E-7</v>
+        <v>0.84525579496840464</v>
       </c>
       <c r="H16">
-        <v>1.0407002516489121E-7</v>
+        <v>0.80993885712889635</v>
       </c>
       <c r="I16">
-        <v>9.9721714710726373E-8</v>
+        <v>0.77609755081511622</v>
       </c>
       <c r="J16">
-        <v>9.5555087731470292E-8</v>
+        <v>0.74367022038722297</v>
       </c>
       <c r="K16">
-        <v>9.1562553029253623E-8</v>
+        <v>0.71259778633488891</v>
       </c>
       <c r="L16">
-        <v>8.7736836585769566E-8</v>
+        <v>0.68282363764005383</v>
       </c>
       <c r="M16">
-        <v>8.4070968309704629E-8</v>
+        <v>0.65429352863703638</v>
       </c>
       <c r="N16">
-        <v>8.0558269337895639E-8</v>
+        <v>0.62695548018209446</v>
       </c>
       <c r="O16">
-        <v>7.7192339867076479E-8</v>
+        <v>0.60075968495237009</v>
       </c>
       <c r="P16">
-        <v>7.3967047494045653E-8</v>
+        <v>0.57565841670168838</v>
       </c>
       <c r="Q16">
-        <v>7.0876516043010981E-8</v>
+        <v>0.55160594330787593</v>
       </c>
       <c r="R16">
-        <v>6.7915114859756758E-8</v>
+        <v>0.52855844345318903</v>
       </c>
       <c r="S16">
-        <v>6.5077448553127356E-8</v>
+        <v>0.50647392678604075</v>
       </c>
       <c r="T16">
-        <v>6.2358347165138043E-8</v>
+        <v>0.48531215741857608</v>
       </c>
       <c r="U16">
-        <v>5.9752856751803507E-8</v>
+        <v>0.46503458062071462</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>0.14641876348184299</v>
+        <v>0.1391141732283461</v>
       </c>
       <c r="B17">
-        <v>1.3609294974081549E-7</v>
+        <v>1.0915744142407799</v>
       </c>
       <c r="C17">
-        <v>1.304066400165843E-7</v>
+        <v>1.0459656577384</v>
       </c>
       <c r="D17">
-        <v>1.2495791878126049E-7</v>
+        <v>1.0022625511326799</v>
       </c>
       <c r="E17">
-        <v>1.1973685898324151E-7</v>
+        <v>0.96038547152207188</v>
       </c>
       <c r="F17">
-        <v>1.147339483483997E-7</v>
+        <v>0.92025812285245445</v>
       </c>
       <c r="G17">
-        <v>1.099400720496241E-7</v>
+        <v>0.88180739691298016</v>
       </c>
       <c r="H17">
-        <v>1.0534649610047279E-7</v>
+        <v>0.84496324013987179</v>
       </c>
       <c r="I17">
-        <v>1.009448514426808E-7</v>
+        <v>0.80965852598549592</v>
       </c>
       <c r="J17">
-        <v>9.6727118698532277E-8</v>
+        <v>0.77582893262018038</v>
       </c>
       <c r="K17">
-        <v>9.268561356031731E-8</v>
+        <v>0.74341282574396172</v>
       </c>
       <c r="L17">
-        <v>8.8812972790254615E-8</v>
+        <v>0.71235114629475549</v>
       </c>
       <c r="M17">
-        <v>8.5102140805372924E-8</v>
+        <v>0.68258730284836455</v>
       </c>
       <c r="N17">
-        <v>8.1546356822910192E-8</v>
+        <v>0.65406706851429008</v>
       </c>
       <c r="O17">
-        <v>7.8139142542810842E-8</v>
+        <v>0.62673848213949679</v>
       </c>
       <c r="P17">
-        <v>7.4874290344879396E-8</v>
+        <v>0.60055175364013702</v>
       </c>
       <c r="Q17">
-        <v>7.1745851979087106E-8</v>
+        <v>0.5754591732887544</v>
       </c>
       <c r="R17">
-        <v>6.874812772842676E-8</v>
+        <v>0.5514150247917029</v>
       </c>
       <c r="S17">
-        <v>6.5875656024570331E-8</v>
+        <v>0.52837550199840766</v>
       </c>
       <c r="T17">
-        <v>6.3123203497411321E-8</v>
+        <v>0.50629862909072854</v>
       </c>
       <c r="U17">
-        <v>6.0485755440362491E-8</v>
+        <v>0.48514418410701349</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>0.1628089241286472</v>
+        <v>0.1569734251968492</v>
       </c>
       <c r="B18">
-        <v>1.3444392769155789E-7</v>
+        <v>1.0859185882602591</v>
       </c>
       <c r="C18">
-        <v>1.2882651830442721E-7</v>
+        <v>1.04054614655841</v>
       </c>
       <c r="D18">
-        <v>1.234438185748054E-7</v>
+        <v>0.99706948091955794</v>
       </c>
       <c r="E18">
-        <v>1.182860217359906E-7</v>
+        <v>0.95540938099605133</v>
       </c>
       <c r="F18">
-        <v>1.1334373077294691E-7</v>
+        <v>0.91548994605011069</v>
       </c>
       <c r="G18">
-        <v>1.086079413018368E-7</v>
+        <v>0.87723844666990825</v>
       </c>
       <c r="H18">
-        <v>1.0407002516489121E-7</v>
+        <v>0.84058519226349981</v>
       </c>
       <c r="I18">
-        <v>9.9721714710726373E-8</v>
+        <v>0.80546340408919848</v>
       </c>
       <c r="J18">
-        <v>9.5555087731470292E-8</v>
+        <v>0.77180909359106065</v>
       </c>
       <c r="K18">
-        <v>9.1562553029253623E-8</v>
+        <v>0.73956094581782761</v>
       </c>
       <c r="L18">
-        <v>8.7736836585769566E-8</v>
+        <v>0.70866020771291782</v>
       </c>
       <c r="M18">
-        <v>8.4070968309704629E-8</v>
+        <v>0.6790505810719486</v>
       </c>
       <c r="N18">
-        <v>8.0558269337895639E-8</v>
+        <v>0.65067811997276559</v>
       </c>
       <c r="O18">
-        <v>7.7192339867076479E-8</v>
+        <v>0.62349113249110599</v>
       </c>
       <c r="P18">
-        <v>7.3967047494045653E-8</v>
+        <v>0.59744008652283098</v>
       </c>
       <c r="Q18">
-        <v>7.0876516043010981E-8</v>
+        <v>0.57247751954114467</v>
       </c>
       <c r="R18">
-        <v>6.7915114859756758E-8</v>
+        <v>0.54855795212438863</v>
       </c>
       <c r="S18">
-        <v>6.5077448553127356E-8</v>
+        <v>0.52563780509686175</v>
       </c>
       <c r="T18">
-        <v>6.2358347165138043E-8</v>
+        <v>0.50367532013170946</v>
       </c>
       <c r="U18">
-        <v>5.9752856751803507E-8</v>
+        <v>0.48263048367122618</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>0.1759210515432148</v>
+        <v>0.16825295275590549</v>
       </c>
       <c r="B19">
-        <v>1.303191620830929E-7</v>
+        <v>1.051983632377129</v>
       </c>
       <c r="C19">
-        <v>1.2487409589841509E-7</v>
+        <v>1.008029079478463</v>
       </c>
       <c r="D19">
-        <v>1.1965653843372609E-7</v>
+        <v>0.96591105964082502</v>
       </c>
       <c r="E19">
-        <v>1.14656983795816E-7</v>
+        <v>0.92555283783992792</v>
       </c>
       <c r="F19">
-        <v>1.098663232718811E-7</v>
+        <v>0.8868808852360478</v>
       </c>
       <c r="G19">
-        <v>1.052758287343153E-7</v>
+        <v>0.84982474521147666</v>
       </c>
       <c r="H19">
-        <v>1.008771367388922E-7</v>
+        <v>0.81431690500526832</v>
       </c>
       <c r="I19">
-        <v>9.6662233287365768E-8</v>
+        <v>0.78029267271141367</v>
       </c>
       <c r="J19">
-        <v>9.2623439226728114E-8</v>
+        <v>0.74769005941634259</v>
       </c>
       <c r="K19">
-        <v>8.8753396258523344E-8</v>
+        <v>0.71644966626102302</v>
       </c>
       <c r="L19">
-        <v>8.5045053532727924E-8</v>
+        <v>0.6865145762218916</v>
       </c>
       <c r="M19">
-        <v>8.149165480177304E-8</v>
+        <v>0.65783025041345244</v>
       </c>
       <c r="N19">
-        <v>7.8086726111304273E-8</v>
+        <v>0.63034442872361884</v>
       </c>
       <c r="O19">
-        <v>7.4824064005253023E-8</v>
+        <v>0.60400703460076099</v>
       </c>
       <c r="P19">
-        <v>7.169772422372966E-8</v>
+        <v>0.57877008381899453</v>
       </c>
       <c r="Q19">
-        <v>6.8702010873147633E-8</v>
+        <v>0.55458759705548577</v>
       </c>
       <c r="R19">
-        <v>6.5831466048847595E-8</v>
+        <v>0.53141551612050331</v>
       </c>
       <c r="S19">
-        <v>6.308085989131424E-8</v>
+        <v>0.50921162368758655</v>
       </c>
       <c r="T19">
-        <v>6.0445181057870036E-8</v>
+        <v>0.48793546637759522</v>
       </c>
       <c r="U19">
-        <v>5.7919627592485751E-8</v>
+        <v>0.46754828105650198</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>0.18903318033637709</v>
+        <v>0.18329232283464519</v>
       </c>
       <c r="B20">
-        <v>1.2454647966803061E-7</v>
+        <v>1.0123928505134689</v>
       </c>
       <c r="C20">
-        <v>1.1934261084305581E-7</v>
+        <v>0.97009250121851609</v>
       </c>
       <c r="D20">
-        <v>1.1435617289866239E-7</v>
+        <v>0.92955956814896179</v>
       </c>
       <c r="E20">
-        <v>1.0957808101941409E-7</v>
+        <v>0.89072020415777597</v>
       </c>
       <c r="F20">
-        <v>1.049996299765793E-7</v>
+        <v>0.85350364761963349</v>
       </c>
       <c r="G20">
-        <v>1.006124782680331E-7</v>
+        <v>0.81784209350996562</v>
       </c>
       <c r="H20">
-        <v>9.6408632920834043E-8</v>
+        <v>0.78367056987065775</v>
       </c>
       <c r="I20">
-        <v>9.2380434928787955E-8</v>
+        <v>0.75092681943732476</v>
       </c>
       <c r="J20">
-        <v>8.8520545298467576E-8</v>
+        <v>0.71955118621249847</v>
       </c>
       <c r="K20">
-        <v>8.4821931678264946E-8</v>
+        <v>0.68948650677807821</v>
       </c>
       <c r="L20">
-        <v>8.1277855546115769E-8</v>
+        <v>0.6606780061490215</v>
       </c>
       <c r="M20">
-        <v>7.7881859932553629E-8</v>
+        <v>0.63307319797853467</v>
       </c>
       <c r="N20">
-        <v>7.4627757656725863E-8</v>
+        <v>0.60662178893294227</v>
       </c>
       <c r="O20">
-        <v>7.1509620053939E-8</v>
+        <v>0.58127558706201998</v>
       </c>
       <c r="P20">
-        <v>6.8521766174195788E-8</v>
+        <v>0.55698841399784693</v>
       </c>
       <c r="Q20">
-        <v>6.5658752432044672E-8</v>
+        <v>0.53371602082221237</v>
       </c>
       <c r="R20">
-        <v>6.2915362688885498E-8</v>
+        <v>0.51141600744929927</v>
       </c>
       <c r="S20">
-        <v>6.0286598749661004E-8</v>
+        <v>0.49004774537676121</v>
       </c>
       <c r="T20">
-        <v>5.7767671256621161E-8</v>
+        <v>0.46957230366445779</v>
       </c>
       <c r="U20">
-        <v>5.535399096356918E-8</v>
+        <v>0.44995237800598642</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>0.203237985954555</v>
+        <v>0.20021161417322819</v>
       </c>
       <c r="B21">
-        <v>1.162980536937611E-7</v>
+        <v>0.96149041668877488</v>
       </c>
       <c r="C21">
-        <v>1.114388250938414E-7</v>
+        <v>0.92131690059859583</v>
       </c>
       <c r="D21">
-        <v>1.067826274289746E-7</v>
+        <v>0.88282193623086247</v>
       </c>
       <c r="E21">
-        <v>1.023209775500886E-7</v>
+        <v>0.8459353894235907</v>
       </c>
       <c r="F21">
-        <v>9.8045746755664663E-8</v>
+        <v>0.81059005639853909</v>
       </c>
       <c r="G21">
-        <v>9.3949145982016726E-8</v>
+        <v>0.77672154132231808</v>
       </c>
       <c r="H21">
-        <v>9.0023711612358482E-8</v>
+        <v>0.74426813898331046</v>
       </c>
       <c r="I21">
-        <v>8.6262291878803967E-8</v>
+        <v>0.7131707223706476</v>
       </c>
       <c r="J21">
-        <v>8.2658033832526845E-8</v>
+        <v>0.68337263495042133</v>
       </c>
       <c r="K21">
-        <v>7.9204370858339915E-8</v>
+        <v>0.65481958744287116</v>
       </c>
       <c r="L21">
-        <v>7.5895010710947021E-8</v>
+        <v>0.62745955891248206</v>
       </c>
       <c r="M21">
-        <v>7.2723924051070858E-8</v>
+        <v>0.60124270199079044</v>
       </c>
       <c r="N21">
-        <v>6.9685333460570613E-8</v>
+        <v>0.57612125205922216</v>
       </c>
       <c r="O21">
-        <v>6.6773702916535869E-8</v>
+        <v>0.55204944022650249</v>
       </c>
       <c r="P21">
-        <v>6.3983727705179626E-8</v>
+        <v>0.52898340994209225</v>
       </c>
       <c r="Q21">
-        <v>6.1310324757154488E-8</v>
+        <v>0.50688113709372407</v>
       </c>
       <c r="R21">
-        <v>5.874862338668424E-8</v>
+        <v>0.48570235344347118</v>
       </c>
       <c r="S21">
-        <v>5.6293956417637602E-8</v>
+        <v>0.4654084732628484</v>
       </c>
       <c r="T21">
-        <v>5.3941851680377537E-8</v>
+        <v>0.44596252303328637</v>
       </c>
       <c r="U21">
-        <v>5.1688023863893823E-8</v>
+        <v>0.42732907408389997</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>0.22072082342637489</v>
+        <v>0.2161909448818895</v>
       </c>
       <c r="B22">
-        <v>1.113487770606673E-7</v>
+        <v>0.89362050492250722</v>
       </c>
       <c r="C22">
-        <v>1.066963418317508E-7</v>
+        <v>0.85628276643869372</v>
       </c>
       <c r="D22">
-        <v>1.022382971846677E-7</v>
+        <v>0.82050509367338864</v>
       </c>
       <c r="E22">
-        <v>9.7966520986288524E-8</v>
+        <v>0.78622230311133623</v>
       </c>
       <c r="F22">
-        <v>9.38732304668725E-8</v>
+        <v>0.75337193477040587</v>
       </c>
       <c r="G22">
-        <v>8.9950968040601557E-8</v>
+        <v>0.72189413840544747</v>
       </c>
       <c r="H22">
-        <v>8.6192587718568668E-8</v>
+        <v>0.69173156446684048</v>
       </c>
       <c r="I22">
-        <v>8.259124208946614E-8</v>
+        <v>0.66282925961507144</v>
       </c>
       <c r="J22">
-        <v>7.9140369844253681E-8</v>
+        <v>0.63513456660097889</v>
       </c>
       <c r="K22">
-        <v>7.5833683822077786E-8</v>
+        <v>0.60859702832925588</v>
       </c>
       <c r="L22">
-        <v>7.2665159555662855E-8</v>
+        <v>0.58316829593042374</v>
       </c>
       <c r="M22">
-        <v>6.9629024295305109E-8</v>
+        <v>0.55880204067379269</v>
       </c>
       <c r="N22">
-        <v>6.6719746491471978E-8</v>
+        <v>0.53545386956092333</v>
       </c>
       <c r="O22">
-        <v>6.3932025716845232E-8</v>
+        <v>0.51308124444580749</v>
       </c>
       <c r="P22">
-        <v>6.1260783009446775E-8</v>
+        <v>0.49164340453441441</v>
       </c>
       <c r="Q22">
-        <v>5.8701151619253091E-8</v>
+        <v>0.47110129212240159</v>
       </c>
       <c r="R22">
-        <v>5.6248468141440082E-8</v>
+        <v>0.45141748143569621</v>
       </c>
       <c r="S22">
-        <v>5.3898264020103012E-8</v>
+        <v>0.43255611044429382</v>
       </c>
       <c r="T22">
-        <v>5.1646257406972898E-8</v>
+        <v>0.41448281552505378</v>
       </c>
       <c r="U22">
-        <v>4.9488345360296582E-8</v>
+        <v>0.39716466885444768</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>0.23601830586956871</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1.031010142319939E-7</v>
+        <v>0.23405019685039269</v>
+      </c>
+      <c r="B23">
+        <v>0.81443894119519966</v>
       </c>
       <c r="C23">
-        <v>9.879319152022218E-8</v>
+        <v>0.78040960991881259</v>
       </c>
       <c r="D23">
-        <v>9.4665360602462285E-8</v>
+        <v>0.74780211068967362</v>
       </c>
       <c r="E23">
-        <v>9.071000096357716E-8</v>
+        <v>0.71655703574704344</v>
       </c>
       <c r="F23">
-        <v>8.6919906314687897E-8</v>
+        <v>0.68661745953758779</v>
       </c>
       <c r="G23">
-        <v>8.3288171464001151E-8</v>
+        <v>0.65792883500243571</v>
       </c>
       <c r="H23">
-        <v>7.980817973620661E-8</v>
+        <v>0.63043889419762922</v>
       </c>
       <c r="I23">
-        <v>7.6473590917524494E-8</v>
+        <v>0.60409755306690305</v>
       </c>
       <c r="J23">
-        <v>7.3278329704439111E-8</v>
+        <v>0.57885682019329954</v>
       </c>
       <c r="K23">
-        <v>7.0216574635074099E-8</v>
+        <v>0.55467070936337459</v>
       </c>
       <c r="L23">
-        <v>6.7282747483042816E-8</v>
+        <v>0.53149515578469209</v>
       </c>
       <c r="M23">
-        <v>6.4471503094450626E-8</v>
+        <v>0.50928793580396503</v>
       </c>
       <c r="N23">
-        <v>6.1777719649533238E-8</v>
+        <v>0.48800858997957758</v>
       </c>
       <c r="O23">
-        <v>5.9196489331188357E-8</v>
+        <v>0.46761834936833269</v>
       </c>
       <c r="P23">
-        <v>5.6723109383400122E-8</v>
+        <v>0.44808006489212637</v>
       </c>
       <c r="Q23">
-        <v>5.4353073543264807E-8</v>
+        <v>0.4293581396558615</v>
       </c>
       <c r="R23">
-        <v>5.2082063831009062E-8</v>
+        <v>0.4114184640932943</v>
       </c>
       <c r="S23">
-        <v>4.9905942683041312E-8</v>
+        <v>0.39422835382264909</v>
       </c>
       <c r="T23">
-        <v>4.7820745413704732E-8</v>
+        <v>0.3777564900987847</v>
       </c>
       <c r="U23">
-        <v>4.5822672991997323E-8</v>
+        <v>0.36197286275342222</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>0.24803775645912049</v>
-      </c>
-      <c r="B24" s="1">
-        <v>9.4852919830522495E-8</v>
+        <v>0.24344980314960571</v>
+      </c>
+      <c r="B24">
+        <v>0.75788068138997755</v>
       </c>
       <c r="C24">
-        <v>9.0889723489850697E-8</v>
+        <v>0.72621449811889516</v>
       </c>
       <c r="D24">
-        <v>8.7092119576515656E-8</v>
+        <v>0.69587140855844654</v>
       </c>
       <c r="E24">
-        <v>8.3453189217558702E-8</v>
+        <v>0.66679613048683217</v>
       </c>
       <c r="F24">
-        <v>7.9966302628138286E-8</v>
+        <v>0.63893569151414442</v>
       </c>
       <c r="G24">
-        <v>7.6625107032692723E-8</v>
+        <v>0.61223933257171126</v>
       </c>
       <c r="H24">
-        <v>7.3423515090787807E-8</v>
+        <v>0.58665841543390518</v>
       </c>
       <c r="I24">
-        <v>7.0355693806561683E-8</v>
+        <v>0.56214633410392378</v>
       </c>
       <c r="J24">
-        <v>6.7416053901561454E-8</v>
+        <v>0.53865842990209833</v>
       </c>
       <c r="K24">
-        <v>6.4599239631609746E-8</v>
+        <v>0.51615191010202932</v>
       </c>
       <c r="L24">
-        <v>6.1900119029148415E-8</v>
+        <v>0.49458576996631082</v>
       </c>
       <c r="M24">
-        <v>5.9313774553282012E-8</v>
+        <v>0.47392071803980079</v>
       </c>
       <c r="N24">
-        <v>5.683549413048625E-8</v>
+        <v>0.4541191045643293</v>
       </c>
       <c r="O24">
-        <v>5.4460762569658367E-8</v>
+        <v>0.43514485288442079</v>
       </c>
       <c r="P24">
-        <v>5.2185253335868732E-8</v>
+        <v>0.4169633937190621</v>
       </c>
       <c r="Q24">
-        <v>5.000482066782559E-8</v>
+        <v>0.39954160217976009</v>
       </c>
       <c r="R24">
-        <v>4.7915492024692943E-8</v>
+        <v>0.38284773742014899</v>
       </c>
       <c r="S24">
-        <v>4.5913460848498768E-8</v>
+        <v>0.36685138480718738</v>
       </c>
       <c r="T24">
-        <v>4.3995079628948837E-8</v>
+        <v>0.35152340050859138</v>
       </c>
       <c r="U24">
-        <v>4.2156853258010009E-8</v>
+        <v>0.3368358583955457</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>0.26114988525228278</v>
-      </c>
-      <c r="B25" s="1">
-        <v>8.4955250758463188E-8</v>
+        <v>0.25284940944881878</v>
+      </c>
+      <c r="B25">
+        <v>0.71263407354579966</v>
       </c>
       <c r="C25">
-        <v>8.1405604215917302E-8</v>
+        <v>0.68285840867896108</v>
       </c>
       <c r="D25">
-        <v>7.8004270937878529E-8</v>
+        <v>0.65432684685346454</v>
       </c>
       <c r="E25">
-        <v>7.4745054018777499E-8</v>
+        <v>0.62698740627866312</v>
       </c>
       <c r="F25">
-        <v>7.1622015475527386E-8</v>
+        <v>0.60079027709538946</v>
       </c>
       <c r="G25">
-        <v>6.8629465429083708E-8</v>
+        <v>0.57568773062713141</v>
       </c>
       <c r="H25">
-        <v>6.5761951738026157E-8</v>
+        <v>0.55163403242292564</v>
       </c>
       <c r="I25">
-        <v>6.3014250065275805E-8</v>
+        <v>0.52858535893354019</v>
       </c>
       <c r="J25">
-        <v>6.0381354359850026E-8</v>
+        <v>0.50649971766913715</v>
       </c>
       <c r="K25">
-        <v>5.7858467736313943E-8</v>
+        <v>0.48533687069295278</v>
       </c>
       <c r="L25">
-        <v>5.5440993735311718E-8</v>
+        <v>0.4650582613116056</v>
       </c>
       <c r="M25">
-        <v>5.3124527949254887E-8</v>
+        <v>0.4456269438284694</v>
       </c>
       <c r="N25">
-        <v>5.0904849997910962E-8</v>
+        <v>0.42700751623213051</v>
       </c>
       <c r="O25">
-        <v>4.8777915839272131E-8</v>
+        <v>0.40916605569729109</v>
       </c>
       <c r="P25">
-        <v>4.6739850401695673E-8</v>
+        <v>0.39207005678061058</v>
       </c>
       <c r="Q25">
-        <v>4.4786940523891992E-8</v>
+        <v>0.37568837219887891</v>
       </c>
       <c r="R25">
-        <v>4.2915628189898268E-8</v>
+        <v>0.35999115608163262</v>
       </c>
       <c r="S25">
-        <v>4.1122504046711833E-8</v>
+        <v>0.34494980959481791</v>
       </c>
       <c r="T25">
-        <v>3.9404301192773482E-8</v>
+        <v>0.33053692883643659</v>
       </c>
       <c r="U25">
-        <v>3.7757889225983653E-8</v>
+        <v>0.31672625490924439</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>0.27426201266685041</v>
-      </c>
-      <c r="B26" s="1">
-        <v>7.7531998954418701E-8</v>
+        <v>0.26318897637795202</v>
+      </c>
+      <c r="B26">
+        <v>0.66173163972109927</v>
       </c>
       <c r="C26">
-        <v>7.4292514760467252E-8</v>
+        <v>0.63408280805903483</v>
       </c>
       <c r="D26">
-        <v>7.1188384458900685E-8</v>
+        <v>0.60758921493535956</v>
       </c>
       <c r="E26">
-        <v>6.8213952619691596E-8</v>
+        <v>0.58220259154447251</v>
       </c>
       <c r="F26">
-        <v>6.5363800111069225E-8</v>
+        <v>0.55787668587428985</v>
       </c>
       <c r="G26">
-        <v>6.2632734226376944E-8</v>
+        <v>0.53456717843947887</v>
       </c>
       <c r="H26">
-        <v>6.001577922345492E-8</v>
+        <v>0.51223160153557357</v>
       </c>
       <c r="I26">
-        <v>5.7508167259311412E-8</v>
+        <v>0.49082926186685838</v>
       </c>
       <c r="J26">
-        <v>5.5105329703566449E-8</v>
+        <v>0.47032116640705568</v>
       </c>
       <c r="K26">
-        <v>5.2802888814842099E-8</v>
+        <v>0.45066995135774163</v>
       </c>
       <c r="L26">
-        <v>5.0596649764934203E-8</v>
+        <v>0.43183981407506211</v>
       </c>
       <c r="M26">
-        <v>4.8482592996234559E-8</v>
+        <v>0.41379644784072128</v>
       </c>
       <c r="N26">
-        <v>4.6456866898479499E-8</v>
+        <v>0.39650697935840662</v>
       </c>
       <c r="O26">
-        <v>4.4515780791482458E-8</v>
+        <v>0.37993990886177009</v>
       </c>
       <c r="P26">
-        <v>4.2655798201065892E-8</v>
+        <v>0.36406505272485251</v>
       </c>
       <c r="Q26">
-        <v>4.0873530415941777E-8</v>
+        <v>0.34885348847038727</v>
       </c>
       <c r="R26">
-        <v>3.9165730313802263E-8</v>
+        <v>0.33427750207580148</v>
       </c>
       <c r="S26">
-        <v>3.7529286445371641E-8</v>
+        <v>0.32031053748090221</v>
       </c>
       <c r="T26">
-        <v>3.5961217365641948E-8</v>
+        <v>0.3069271482052624</v>
       </c>
       <c r="U26">
-        <v>3.4458666201963879E-8</v>
+        <v>0.29410295098715528</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>0.28081807775272882</v>
-      </c>
-      <c r="B27" s="1">
-        <v>7.0933479223535152E-8</v>
+        <v>0.27916830708661339</v>
+      </c>
+      <c r="B27">
+        <v>0.58820590197431077</v>
       </c>
       <c r="C27">
-        <v>6.7969697973657668E-8</v>
+        <v>0.56362916271914232</v>
       </c>
       <c r="D27">
-        <v>6.5129751045644552E-8</v>
+        <v>0.54007930216476419</v>
       </c>
       <c r="E27">
-        <v>6.2408464326435898E-8</v>
+        <v>0.51751341470619794</v>
       </c>
       <c r="F27">
-        <v>5.9800879890580848E-8</v>
+        <v>0.49589038744381342</v>
       </c>
       <c r="G27">
-        <v>5.7302246967369143E-8</v>
+        <v>0.47517082527953691</v>
       </c>
       <c r="H27">
-        <v>5.4908013285378971E-8</v>
+        <v>0.45531697914273223</v>
       </c>
       <c r="I27">
-        <v>5.2613816778671682E-8</v>
+        <v>0.43629267721498538</v>
       </c>
       <c r="J27">
-        <v>5.0415477639522582E-8</v>
+        <v>0.41806325902849401</v>
       </c>
       <c r="K27">
-        <v>4.8308990703209191E-8</v>
+        <v>0.40059551231799267</v>
       </c>
       <c r="L27">
-        <v>4.62905181509821E-8</v>
+        <v>0.3838576125111664</v>
       </c>
       <c r="M27">
-        <v>4.4356382517924443E-8</v>
+        <v>0.36781906474730802</v>
       </c>
       <c r="N27">
-        <v>4.2503059992960812E-8</v>
+        <v>0.3524506483185838</v>
       </c>
       <c r="O27">
-        <v>4.0727173998808702E-8</v>
+        <v>0.33772436343268469</v>
       </c>
       <c r="P27">
-        <v>3.9025489040176143E-8</v>
+        <v>0.32361338019986902</v>
       </c>
       <c r="Q27">
-        <v>3.7394904808996947E-8</v>
+        <v>0.31009198975145552</v>
       </c>
       <c r="R27">
-        <v>3.5832450535964667E-8</v>
+        <v>0.29713555740071251</v>
       </c>
       <c r="S27">
-        <v>3.4335279578073499E-8</v>
+        <v>0.28472047776080212</v>
       </c>
       <c r="T27">
-        <v>3.2900664232305552E-8</v>
+        <v>0.27282413173801112</v>
       </c>
       <c r="U27">
-        <v>3.1525990766015633E-8</v>
+        <v>0.26142484532191601</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>0.2906521733136545</v>
-      </c>
-      <c r="B28" s="1">
-        <v>6.5984644687505486E-8</v>
+        <v>0.28762795275590491</v>
+      </c>
+      <c r="B28">
+        <v>0.53164764216908877</v>
       </c>
       <c r="C28">
-        <v>6.3227638336690964E-8</v>
+        <v>0.509434050919225</v>
       </c>
       <c r="D28">
-        <v>6.0585826726325976E-8</v>
+        <v>0.48814860003353711</v>
       </c>
       <c r="E28">
-        <v>5.8054396727045283E-8</v>
+        <v>0.46775250944598679</v>
       </c>
       <c r="F28">
-        <v>5.5628736314275392E-8</v>
+        <v>0.44820861942036988</v>
       </c>
       <c r="G28">
-        <v>5.3304426165564622E-8</v>
+        <v>0.42948132284881241</v>
       </c>
       <c r="H28">
-        <v>5.1077231608998139E-8</v>
+        <v>0.41153650037900807</v>
       </c>
       <c r="I28">
-        <v>4.894309490802873E-8</v>
+        <v>0.39434145825200623</v>
       </c>
       <c r="J28">
-        <v>4.6898127868666862E-8</v>
+        <v>0.37786486873729291</v>
       </c>
       <c r="K28">
-        <v>4.4938604755561279E-8</v>
+        <v>0.3620767130566474</v>
       </c>
       <c r="L28">
-        <v>4.3060955504063748E-8</v>
+        <v>0.34694822669278508</v>
       </c>
       <c r="M28">
-        <v>4.1261759215910877E-8</v>
+        <v>0.33245184698314389</v>
       </c>
       <c r="N28">
-        <v>3.9537737926673161E-8</v>
+        <v>0.31856116290333553</v>
       </c>
       <c r="O28">
-        <v>3.7885750633615577E-8</v>
+        <v>0.30525086694877279</v>
       </c>
       <c r="P28">
-        <v>3.6302787573089607E-8</v>
+        <v>0.2924967090268048</v>
       </c>
       <c r="Q28">
-        <v>3.4785964737030128E-8</v>
+        <v>0.28027545227535411</v>
       </c>
       <c r="R28">
-        <v>3.3332518618567333E-8</v>
+        <v>0.26856483072756721</v>
       </c>
       <c r="S28">
-        <v>3.1939801177180029E-8</v>
+        <v>0.25734350874534051</v>
       </c>
       <c r="T28">
-        <v>3.0605275014217858E-8</v>
+        <v>0.24659104214781791</v>
       </c>
       <c r="U28">
-        <v>2.9326508750002448E-8</v>
+        <v>0.23628784096403951</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>0.29939359204956451</v>
-      </c>
-      <c r="B29" s="1">
-        <v>5.6911707688607091E-8</v>
+        <v>0.29420767716535462</v>
+      </c>
+      <c r="B29">
+        <v>0.46943355638334427</v>
       </c>
       <c r="C29">
-        <v>5.4533791731398028E-8</v>
+        <v>0.44981942793931567</v>
       </c>
       <c r="D29">
-        <v>5.2255231153410562E-8</v>
+        <v>0.43102482768918698</v>
       </c>
       <c r="E29">
-        <v>5.0071874634094277E-8</v>
+        <v>0.41301551365975431</v>
       </c>
       <c r="F29">
-        <v>4.7979744305634297E-8</v>
+        <v>0.39575867459458203</v>
       </c>
       <c r="G29">
-        <v>4.5975028505654577E-8</v>
+        <v>0.37922287017501521</v>
       </c>
       <c r="H29">
-        <v>4.4054074832731778E-8</v>
+        <v>0.3633779737389114</v>
       </c>
       <c r="I29">
-        <v>4.2213383492067527E-8</v>
+        <v>0.3481951173927289</v>
       </c>
       <c r="J29">
-        <v>4.0449600919195132E-8</v>
+        <v>0.33364663941697131</v>
       </c>
       <c r="K29">
-        <v>3.8759513670104432E-8</v>
+        <v>0.31970603386916741</v>
       </c>
       <c r="L29">
-        <v>3.7140042566652469E-8</v>
+        <v>0.30634790229256559</v>
       </c>
       <c r="M29">
-        <v>3.5588237086593992E-8</v>
+        <v>0.29354790744256321</v>
       </c>
       <c r="N29">
-        <v>3.4101269988010648E-8</v>
+        <v>0.28128272894656209</v>
       </c>
       <c r="O29">
-        <v>3.2676432158345272E-8</v>
+        <v>0.2695300208164696</v>
       </c>
       <c r="P29">
-        <v>3.13111276786566E-8</v>
+        <v>0.25826837073643399</v>
       </c>
       <c r="Q29">
-        <v>3.0002869094101901E-8</v>
+        <v>0.24747726105164239</v>
       </c>
       <c r="R29">
-        <v>2.874927288203108E-8</v>
+        <v>0.23713703138710721</v>
       </c>
       <c r="S29">
-        <v>2.7548055109435149E-8</v>
+        <v>0.2272288428283325</v>
       </c>
       <c r="T29">
-        <v>2.6397027271837619E-8</v>
+        <v>0.21773464359860509</v>
       </c>
       <c r="U29">
-        <v>2.5294092306047609E-8</v>
+        <v>0.2086371361703753</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>0.31250572084272671</v>
-      </c>
-      <c r="B30" s="1">
-        <v>4.8663723811401678E-8</v>
+        <v>0.30360728346456628</v>
+      </c>
+      <c r="B30">
+        <v>0.40156364461707739</v>
       </c>
       <c r="C30">
-        <v>4.6630429607307498E-8</v>
+        <v>0.38478529377941428</v>
       </c>
       <c r="D30">
-        <v>4.4682091608710998E-8</v>
+        <v>0.36870798513171388</v>
       </c>
       <c r="E30">
-        <v>4.2815160129178177E-8</v>
+        <v>0.35330242734750039</v>
       </c>
       <c r="F30">
-        <v>4.1026233797206331E-8</v>
+        <v>0.33854055296644942</v>
       </c>
       <c r="G30">
-        <v>3.9312053359248817E-8</v>
+        <v>0.32439546725814522</v>
       </c>
       <c r="H30">
-        <v>3.7669495741665239E-8</v>
+        <v>0.31084139922244203</v>
       </c>
       <c r="I30">
-        <v>3.609556836077844E-8</v>
+        <v>0.29785365463715341</v>
       </c>
       <c r="J30">
-        <v>3.4587403670671837E-8</v>
+        <v>0.28540857106752948</v>
       </c>
       <c r="K30">
-        <v>3.3142253938793632E-8</v>
+        <v>0.27348347475555262</v>
       </c>
       <c r="L30">
-        <v>3.1757486239849523E-8</v>
+        <v>0.26205663931050782</v>
       </c>
       <c r="M30">
-        <v>3.0430577658863417E-8</v>
+        <v>0.2511072461255659</v>
       </c>
       <c r="N30">
-        <v>2.9159110694666409E-8</v>
+        <v>0.24061534644826391</v>
       </c>
       <c r="O30">
-        <v>2.7940768855439651E-8</v>
+        <v>0.23056182503577499</v>
       </c>
       <c r="P30">
-        <v>2.677333243828678E-8</v>
+        <v>0.22092836532875659</v>
       </c>
       <c r="Q30">
-        <v>2.5654674485146319E-8</v>
+        <v>0.2116974160803205</v>
       </c>
       <c r="R30">
-        <v>2.4582756907676659E-8</v>
+        <v>0.20285215937933249</v>
       </c>
       <c r="S30">
-        <v>2.3555626774052889E-8</v>
+        <v>0.19437648000977831</v>
       </c>
       <c r="T30">
-        <v>2.257141275091097E-8</v>
+        <v>0.18625493609037291</v>
       </c>
       <c r="U30">
-        <v>2.1628321693956309E-8</v>
+        <v>0.17847273094092331</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>0.32452517143227849</v>
-      </c>
-      <c r="B31" s="1">
-        <v>4.2890046677945077E-8</v>
+        <v>0.3214665354330708</v>
+      </c>
+      <c r="B31">
+        <v>0.35631703677289939</v>
       </c>
       <c r="C31">
-        <v>4.1097991395419367E-8</v>
+        <v>0.34142920433948021</v>
       </c>
       <c r="D31">
-        <v>3.9380812742423657E-8</v>
+        <v>0.32716342342673188</v>
       </c>
       <c r="E31">
-        <v>3.7735382182855027E-8</v>
+        <v>0.31349370313933123</v>
       </c>
       <c r="F31">
-        <v>3.6158701898809418E-8</v>
+        <v>0.30039513854769428</v>
       </c>
       <c r="G31">
-        <v>3.4647899328842673E-8</v>
+        <v>0.28784386531356537</v>
       </c>
       <c r="H31">
-        <v>3.3200221934436848E-8</v>
+        <v>0.27581701621146248</v>
       </c>
       <c r="I31">
-        <v>3.1813032185137108E-8</v>
+        <v>0.26429267946676982</v>
       </c>
       <c r="J31">
-        <v>3.048380275322205E-8</v>
+        <v>0.25324985883456819</v>
       </c>
       <c r="K31">
-        <v>2.9210111909153219E-8</v>
+        <v>0.24266843534647611</v>
       </c>
       <c r="L31">
-        <v>2.7989639109414302E-8</v>
+        <v>0.2325291306558025</v>
       </c>
       <c r="M31">
-        <v>2.682016076870159E-8</v>
+        <v>0.2228134719142344</v>
       </c>
       <c r="N31">
-        <v>2.569954620876324E-8</v>
+        <v>0.21350375811606501</v>
       </c>
       <c r="O31">
-        <v>2.462575377650622E-8</v>
+        <v>0.20458302784864529</v>
       </c>
       <c r="P31">
-        <v>2.3596827124298641E-8</v>
+        <v>0.19603502839030501</v>
       </c>
       <c r="Q31">
-        <v>2.2610891645690501E-8</v>
+        <v>0.1878441860994392</v>
       </c>
       <c r="R31">
-        <v>2.1666151060059201E-8</v>
+        <v>0.17999557804081609</v>
       </c>
       <c r="S31">
-        <v>2.0760884139957089E-8</v>
+        <v>0.17247490479740879</v>
       </c>
       <c r="T31">
-        <v>1.9893441575198922E-8</v>
+        <v>0.1652684644182181</v>
       </c>
       <c r="U31">
-        <v>1.906224296797559E-8</v>
+        <v>0.158363127454622</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>0.33763729884684618</v>
-      </c>
-      <c r="B32" s="1">
-        <v>3.7941212141915417E-8</v>
+        <v>0.33838582677165369</v>
+      </c>
+      <c r="B32">
+        <v>0.28844712500663328</v>
       </c>
       <c r="C32">
-        <v>3.635593175845267E-8</v>
+        <v>0.27639507017957959</v>
       </c>
       <c r="D32">
-        <v>3.48368884231051E-8</v>
+        <v>0.26484658086925961</v>
       </c>
       <c r="E32">
-        <v>3.3381314583464432E-8</v>
+        <v>0.25378061682707798</v>
       </c>
       <c r="F32">
-        <v>3.1986558322503982E-8</v>
+        <v>0.24317701691956251</v>
       </c>
       <c r="G32">
-        <v>3.0650078527038159E-8</v>
+        <v>0.23301646239669621</v>
       </c>
       <c r="H32">
-        <v>2.936944025805603E-8</v>
+        <v>0.22328044169499381</v>
       </c>
       <c r="I32">
-        <v>2.8142310314494169E-8</v>
+        <v>0.21395121671119491</v>
       </c>
       <c r="J32">
-        <v>2.6966452982366329E-8</v>
+        <v>0.20501179048512699</v>
       </c>
       <c r="K32">
-        <v>2.5839725961505321E-8</v>
+        <v>0.19644587623286189</v>
       </c>
       <c r="L32">
-        <v>2.476007646249595E-8</v>
+        <v>0.1882378676737452</v>
       </c>
       <c r="M32">
-        <v>2.372553746668803E-8</v>
+        <v>0.1803728105972377</v>
       </c>
       <c r="N32">
-        <v>2.2734224142475599E-8</v>
+        <v>0.17283637561776721</v>
       </c>
       <c r="O32">
-        <v>2.1784330411313099E-8</v>
+        <v>0.1656148320679513</v>
       </c>
       <c r="P32">
-        <v>2.0874125657212122E-8</v>
+        <v>0.15869502298262819</v>
       </c>
       <c r="Q32">
-        <v>2.0001951573723698E-8</v>
+        <v>0.1520643411281177</v>
       </c>
       <c r="R32">
-        <v>1.916621914266186E-8</v>
+        <v>0.14571070603304179</v>
       </c>
       <c r="S32">
-        <v>1.8365405739063619E-8</v>
+        <v>0.13962254197885501</v>
       </c>
       <c r="T32">
-        <v>1.7598052357111241E-8</v>
+        <v>0.13378875690998629</v>
       </c>
       <c r="U32">
-        <v>1.6862760951962409E-8</v>
+        <v>0.1281987222251704</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>0.34965675081499259</v>
-      </c>
-      <c r="B33" s="1">
-        <v>3.2167535008458803E-8</v>
+        <v>0.34966535433070861</v>
+      </c>
+      <c r="B33">
+        <v>0.23754469118193289</v>
       </c>
       <c r="C33">
-        <v>3.0823493546564532E-8</v>
+        <v>0.2276194695596534</v>
       </c>
       <c r="D33">
-        <v>2.9535609556817749E-8</v>
+        <v>0.2181089489511546</v>
       </c>
       <c r="E33">
-        <v>2.8301536637141269E-8</v>
+        <v>0.2089958020928874</v>
       </c>
       <c r="F33">
-        <v>2.7119026424107069E-8</v>
+        <v>0.20026342569846289</v>
       </c>
       <c r="G33">
-        <v>2.5985924496632001E-8</v>
+        <v>0.19189591020904359</v>
       </c>
       <c r="H33">
-        <v>2.4900166450827639E-8</v>
+        <v>0.18387801080764171</v>
       </c>
       <c r="I33">
-        <v>2.3859774138852831E-8</v>
+        <v>0.1761951196445132</v>
       </c>
       <c r="J33">
-        <v>2.2862852064916539E-8</v>
+        <v>0.16883323922304549</v>
       </c>
       <c r="K33">
-        <v>2.1907583931864921E-8</v>
+        <v>0.16177895689765071</v>
       </c>
       <c r="L33">
-        <v>2.0992229332060719E-8</v>
+        <v>0.15501942043720171</v>
       </c>
       <c r="M33">
-        <v>2.011512057652619E-8</v>
+        <v>0.14854231460948961</v>
       </c>
       <c r="N33">
-        <v>1.927465965657243E-8</v>
+        <v>0.14233583874404329</v>
       </c>
       <c r="O33">
-        <v>1.8469315332379668E-8</v>
+        <v>0.1363886852324302</v>
       </c>
       <c r="P33">
-        <v>1.7697620343223989E-8</v>
+        <v>0.13069001892686999</v>
       </c>
       <c r="Q33">
-        <v>1.6958168734267871E-8</v>
+        <v>0.1252294573996261</v>
       </c>
       <c r="R33">
-        <v>1.6249613295044391E-8</v>
+        <v>0.1199970520272107</v>
       </c>
       <c r="S33">
-        <v>1.557066310496782E-8</v>
+        <v>0.1149832698649392</v>
       </c>
       <c r="T33">
-        <v>1.492008118139919E-8</v>
+        <v>0.1101789762788121</v>
       </c>
       <c r="U33">
-        <v>1.429668222598169E-8</v>
+        <v>0.1055754183030813</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>0.36604691008320223</v>
-      </c>
-      <c r="B34" s="1">
-        <v>2.721870047242915E-8</v>
+        <v>0.36376476377952682</v>
+      </c>
+      <c r="B34">
+        <v>0.22057721324036639</v>
       </c>
       <c r="C34">
-        <v>2.6081433909597831E-8</v>
+        <v>0.21136093601967831</v>
       </c>
       <c r="D34">
-        <v>2.499168523749918E-8</v>
+        <v>0.2025297383117865</v>
       </c>
       <c r="E34">
-        <v>2.394746903775067E-8</v>
+        <v>0.19406753051482409</v>
       </c>
       <c r="F34">
-        <v>2.2946882847801619E-8</v>
+        <v>0.18595889529142989</v>
       </c>
       <c r="G34">
-        <v>2.198810369482749E-8</v>
+        <v>0.17818905947982619</v>
       </c>
       <c r="H34">
-        <v>2.1069384774446811E-8</v>
+        <v>0.17074386717852449</v>
       </c>
       <c r="I34">
-        <v>2.0189052268209889E-8</v>
+        <v>0.1636097539556195</v>
       </c>
       <c r="J34">
-        <v>1.9345502294060819E-8</v>
+        <v>0.15677372213568519</v>
       </c>
       <c r="K34">
-        <v>1.8537197984217019E-8</v>
+        <v>0.15022331711924719</v>
       </c>
       <c r="L34">
-        <v>1.776266668514237E-8</v>
+        <v>0.14394660469168741</v>
       </c>
       <c r="M34">
-        <v>1.7020497274512631E-8</v>
+        <v>0.13793214928024039</v>
       </c>
       <c r="N34">
-        <v>1.6309337590284789E-8</v>
+        <v>0.13216899311946889</v>
       </c>
       <c r="O34">
-        <v>1.562789196718655E-8</v>
+        <v>0.1266466362872567</v>
       </c>
       <c r="P34">
-        <v>1.497491887613746E-8</v>
+        <v>0.1213550175749508</v>
       </c>
       <c r="Q34">
-        <v>1.434922866230107E-8</v>
+        <v>0.1162844961567957</v>
       </c>
       <c r="R34">
-        <v>1.374968137764706E-8</v>
+        <v>0.11142583402526721</v>
       </c>
       <c r="S34">
-        <v>1.3175184704074351E-8</v>
+        <v>0.1067701791603007</v>
       </c>
       <c r="T34">
-        <v>1.2624691963311511E-8</v>
+        <v>0.1023090494017541</v>
       </c>
       <c r="U34">
-        <v>1.2097200209968511E-8</v>
+        <v>9.8034316995718435E-2</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>0.383529747555022</v>
-      </c>
-      <c r="B35" s="1">
-        <v>2.3919440606987369E-8</v>
+        <v>0.37786417322834631</v>
+      </c>
+      <c r="B35">
+        <v>0.18098643137671089</v>
       </c>
       <c r="C35">
-        <v>2.2920025516193039E-8</v>
+        <v>0.17342435775973611</v>
       </c>
       <c r="D35">
-        <v>2.196236853087111E-8</v>
+        <v>0.16617824681992741</v>
       </c>
       <c r="E35">
-        <v>2.1044724891122811E-8</v>
+        <v>0.15923489683267619</v>
       </c>
       <c r="F35">
-        <v>2.0165422737557441E-8</v>
+        <v>0.15258165767501941</v>
       </c>
       <c r="G35">
-        <v>1.932286006532359E-8</v>
+        <v>0.146206407778319</v>
       </c>
       <c r="H35">
-        <v>1.851550180540884E-8</v>
+        <v>0.14009753204391759</v>
       </c>
       <c r="I35">
-        <v>1.774187702789002E-8</v>
+        <v>0.13424390068153391</v>
       </c>
       <c r="J35">
-        <v>1.7000576262038879E-8</v>
+        <v>0.12863484893184429</v>
       </c>
       <c r="K35">
-        <v>1.6290248928400559E-8</v>
+        <v>0.12326015763630541</v>
       </c>
       <c r="L35">
-        <v>1.5609600878166328E-8</v>
+        <v>0.1181100346188204</v>
       </c>
       <c r="M35">
-        <v>1.4957392035357569E-8</v>
+        <v>0.11317509684532551</v>
       </c>
       <c r="N35">
-        <v>1.4332434137525441E-8</v>
+        <v>0.108446353328795</v>
       </c>
       <c r="O35">
-        <v>1.3733588570849671E-8</v>
+        <v>0.10391518874851829</v>
       </c>
       <c r="P35">
-        <v>1.315976429569258E-8</v>
+        <v>9.9573347753805802E-2</v>
       </c>
       <c r="Q35">
-        <v>1.260991585882865E-8</v>
+        <v>9.5412919923524714E-2</v>
       </c>
       <c r="R35">
-        <v>1.2083041488728269E-8</v>
+        <v>9.1426325354065363E-2</v>
       </c>
       <c r="S35">
-        <v>1.157818127042528E-8</v>
+        <v>8.7606300849477528E-2</v>
       </c>
       <c r="T35">
-        <v>1.1094415396643299E-8</v>
+        <v>8.3945886688618784E-2</v>
       </c>
       <c r="U35">
-        <v>1.0630862491994391E-8</v>
+        <v>8.0438413945204873E-2</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>0.3955491981445739</v>
-      </c>
-      <c r="B36" s="1">
-        <v>2.0620180741545581E-8</v>
+        <v>0.39384350393700768</v>
+      </c>
+      <c r="B36">
+        <v>0.16401895343514439</v>
       </c>
       <c r="C36">
-        <v>1.9758617122788241E-8</v>
+        <v>0.15716582421976091</v>
       </c>
       <c r="D36">
-        <v>1.8933051824243041E-8</v>
+        <v>0.15059903618055931</v>
       </c>
       <c r="E36">
-        <v>1.8141980744494958E-8</v>
+        <v>0.14430662525461299</v>
       </c>
       <c r="F36">
-        <v>1.7383962627313249E-8</v>
+        <v>0.13827712726798649</v>
       </c>
       <c r="G36">
-        <v>1.6657616435819699E-8</v>
+        <v>0.13249955704910171</v>
       </c>
       <c r="H36">
-        <v>1.5961618836370869E-8</v>
+        <v>0.1269633884148004</v>
       </c>
       <c r="I36">
-        <v>1.5294701787570159E-8</v>
+        <v>0.1216585349926402</v>
       </c>
       <c r="J36">
-        <v>1.465565023001695E-8</v>
+        <v>0.116575331844484</v>
       </c>
       <c r="K36">
-        <v>1.4043299872584109E-8</v>
+        <v>0.11170451785790191</v>
       </c>
       <c r="L36">
-        <v>1.345653507119027E-8</v>
+        <v>0.1070372188733061</v>
       </c>
       <c r="M36">
-        <v>1.289428679620252E-8</v>
+        <v>0.1025649315160763</v>
       </c>
       <c r="N36">
-        <v>1.23555306847661E-8</v>
+        <v>9.8279507704220531E-2</v>
       </c>
       <c r="O36">
-        <v>1.1839285174512799E-8</v>
+        <v>9.4173139803344824E-2</v>
       </c>
       <c r="P36">
-        <v>1.1344609715247709E-8</v>
+        <v>9.0238346401886591E-2</v>
       </c>
       <c r="Q36">
-        <v>1.087060305535623E-8</v>
+        <v>8.646795868069436E-2</v>
       </c>
       <c r="R36">
-        <v>1.041640159980947E-8</v>
+        <v>8.2855107352121815E-2</v>
       </c>
       <c r="S36">
-        <v>9.9811778367762041E-9</v>
+        <v>7.9393210144839077E-2</v>
       </c>
       <c r="T36">
-        <v>9.5641388299750981E-9</v>
+        <v>7.6075959811560845E-2</v>
       </c>
       <c r="U36">
-        <v>9.1645247740202608E-9</v>
+        <v>7.2897312637841993E-2</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>0.41084668196636231</v>
-      </c>
-      <c r="B37" s="1">
-        <v>1.5671346205515921E-8</v>
+        <v>0.40324311023622078</v>
+      </c>
+      <c r="B37">
+        <v>0.135739823532533</v>
       </c>
       <c r="C37">
-        <v>1.501655748582154E-8</v>
+        <v>0.13006826831980181</v>
       </c>
       <c r="D37">
-        <v>1.4389127504924481E-8</v>
+        <v>0.12463368511494539</v>
       </c>
       <c r="E37">
-        <v>1.378791314510436E-8</v>
+        <v>0.119426172624507</v>
       </c>
       <c r="F37">
-        <v>1.3211819051007799E-8</v>
+        <v>0.11443624325626441</v>
       </c>
       <c r="G37">
-        <v>1.265979563401518E-8</v>
+        <v>0.1096548058337391</v>
       </c>
       <c r="H37">
-        <v>1.213083715999004E-8</v>
+        <v>0.105073149032938</v>
       </c>
       <c r="I37">
-        <v>1.162397991692721E-8</v>
+        <v>0.1006829255111503</v>
       </c>
       <c r="J37">
-        <v>1.113830045916123E-8</v>
+        <v>9.6476136698883067E-2</v>
       </c>
       <c r="K37">
-        <v>1.067291392493621E-8</v>
+        <v>9.2445118227228923E-2</v>
       </c>
       <c r="L37">
-        <v>1.022697242427192E-8</v>
+        <v>8.8582525964115158E-2</v>
       </c>
       <c r="M37">
-        <v>9.7996634941889556E-9</v>
+        <v>8.4881322633993991E-2</v>
       </c>
       <c r="N37">
-        <v>9.3902086184784542E-9</v>
+        <v>8.1334764996596101E-2</v>
       </c>
       <c r="O37">
-        <v>8.9978618093196764E-9</v>
+        <v>7.7936391561388624E-2</v>
       </c>
       <c r="P37">
-        <v>8.6219082481611849E-9</v>
+        <v>7.4680010815354234E-2</v>
       </c>
       <c r="Q37">
-        <v>8.261662983389429E-9</v>
+        <v>7.1559689942643431E-2</v>
       </c>
       <c r="R37">
-        <v>7.9164696824121355E-9</v>
+        <v>6.8569744015548911E-2</v>
       </c>
       <c r="S37">
-        <v>7.5856994358827387E-9</v>
+        <v>6.5704725637108038E-2</v>
       </c>
       <c r="T37">
-        <v>7.2687496118874126E-9</v>
+        <v>6.2959415016463988E-2</v>
       </c>
       <c r="U37">
-        <v>6.9650427580070796E-9</v>
+        <v>6.0328810458903571E-2</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>0.4228661325559141</v>
-      </c>
-      <c r="B38" s="1">
-        <v>1.402177153492805E-8</v>
+        <v>0.41922244094488209</v>
+      </c>
+      <c r="B38">
+        <v>0.1018048676494</v>
       </c>
       <c r="C38">
-        <v>1.343590624225963E-8</v>
+        <v>9.7551201239851573E-2</v>
       </c>
       <c r="D38">
-        <v>1.287451989223398E-8</v>
+        <v>9.3475263836209202E-2</v>
       </c>
       <c r="E38">
-        <v>1.2336589692341609E-8</v>
+        <v>8.9569629468380429E-2</v>
       </c>
       <c r="F38">
-        <v>1.1821135584946549E-8</v>
+        <v>8.5827182442198474E-2</v>
       </c>
       <c r="G38">
-        <v>1.132721846171457E-8</v>
+        <v>8.2241104375304463E-2</v>
       </c>
       <c r="H38">
-        <v>1.085393845264718E-8</v>
+        <v>7.8804861774703652E-2</v>
       </c>
       <c r="I38">
-        <v>1.040043328660414E-8</v>
+        <v>7.5512194133362881E-2</v>
       </c>
       <c r="J38">
-        <v>9.9658767203274442E-9</v>
+        <v>7.2357102524162442E-2</v>
       </c>
       <c r="K38">
-        <v>9.5494770331047573E-9</v>
+        <v>6.9333838670421824E-2</v>
       </c>
       <c r="L38">
-        <v>9.1504755843296261E-9</v>
+        <v>6.6436894473086511E-2</v>
       </c>
       <c r="M38">
-        <v>8.7681454313304529E-9</v>
+        <v>6.3660991975495629E-2</v>
       </c>
       <c r="N38">
-        <v>8.4017900049501571E-9</v>
+        <v>6.1001073747447197E-2</v>
       </c>
       <c r="O38">
-        <v>8.0507418404634298E-9</v>
+        <v>5.8452293671041593E-2</v>
       </c>
       <c r="P38">
-        <v>7.7143613615195379E-9</v>
+        <v>5.6010008111515797E-2</v>
       </c>
       <c r="Q38">
-        <v>7.3920357148950453E-9</v>
+        <v>5.3669767456982688E-2</v>
       </c>
       <c r="R38">
-        <v>7.0831776539335929E-9</v>
+        <v>5.1427308011661788E-2</v>
       </c>
       <c r="S38">
-        <v>6.787224468638344E-9</v>
+        <v>4.9278544227831143E-2</v>
       </c>
       <c r="T38">
-        <v>6.5036369604679334E-9</v>
+        <v>4.7219561262348088E-2</v>
       </c>
       <c r="U38">
-        <v>6.231898459968025E-9</v>
+        <v>4.5246607844177771E-2</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>0.43597825997048179</v>
-      </c>
-      <c r="B39" s="1">
-        <v>7.4232739088976917E-9</v>
+        <v>0.43990157480315001</v>
+      </c>
+      <c r="B39">
+        <v>5.0902433824699979E-2</v>
       </c>
       <c r="C39">
-        <v>7.1131106367062466E-9</v>
+        <v>4.8775600619925787E-2</v>
       </c>
       <c r="D39">
-        <v>6.8159067752272622E-9</v>
+        <v>4.6737631918104601E-2</v>
       </c>
       <c r="E39">
-        <v>6.5311208473063744E-9</v>
+        <v>4.4784814734190208E-2</v>
       </c>
       <c r="F39">
-        <v>6.2582340000825028E-9</v>
+        <v>4.2913591221099237E-2</v>
       </c>
       <c r="G39">
-        <v>5.9967490596873042E-9</v>
+        <v>4.1120552187652232E-2</v>
       </c>
       <c r="H39">
-        <v>5.7461896254416949E-9</v>
+        <v>3.9402430887351833E-2</v>
       </c>
       <c r="I39">
-        <v>5.5060992018991554E-9</v>
+        <v>3.775609706668144E-2</v>
       </c>
       <c r="J39">
-        <v>5.2760403671544521E-9</v>
+        <v>3.6178551262081221E-2</v>
       </c>
       <c r="K39">
-        <v>5.0555939759025632E-9</v>
+        <v>3.4666919335210912E-2</v>
       </c>
       <c r="L39">
-        <v>4.8443583957958152E-9</v>
+        <v>3.3218447236543262E-2</v>
       </c>
       <c r="M39">
-        <v>4.6419487757079509E-9</v>
+        <v>3.1830495987747807E-2</v>
       </c>
       <c r="N39">
-        <v>4.4479963445720152E-9</v>
+        <v>3.0500536873723599E-2</v>
       </c>
       <c r="O39">
-        <v>4.262147739514558E-9</v>
+        <v>2.92261468355208E-2</v>
       </c>
       <c r="P39">
-        <v>4.0840643620621018E-9</v>
+        <v>2.8005004055757898E-2</v>
       </c>
       <c r="Q39">
-        <v>3.9134217612469362E-9</v>
+        <v>2.6834883728491341E-2</v>
       </c>
       <c r="R39">
-        <v>3.7499090424883468E-9</v>
+        <v>2.571365400583089E-2</v>
       </c>
       <c r="S39">
-        <v>3.5932283011722571E-9</v>
+        <v>2.4639272113915572E-2</v>
       </c>
       <c r="T39">
-        <v>3.4430940798973749E-9</v>
+        <v>2.360978063117404E-2</v>
       </c>
       <c r="U39">
-        <v>3.299232848398975E-9</v>
+        <v>2.2623303922088889E-2</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>0.44909038876364388</v>
-      </c>
-      <c r="B40" s="1">
-        <v>2.474428320441432E-9</v>
+        <v>0.44648129921259833</v>
+      </c>
+      <c r="B40">
+        <v>1.6967477941566601E-2</v>
       </c>
       <c r="C40">
-        <v>2.371040409111448E-9</v>
+        <v>1.6258533539975209E-2</v>
       </c>
       <c r="D40">
-        <v>2.2719723077839899E-9</v>
+        <v>1.557921063936815E-2</v>
       </c>
       <c r="E40">
-        <v>2.1770435238055372E-9</v>
+        <v>1.4928271578063351E-2</v>
       </c>
       <c r="F40">
-        <v>2.0860811059648898E-9</v>
+        <v>1.430453040703303E-2</v>
       </c>
       <c r="G40">
-        <v>1.9989193293925232E-9</v>
+        <v>1.370685072921737E-2</v>
       </c>
       <c r="H40">
-        <v>1.9153993936256399E-9</v>
+        <v>1.313414362911723E-2</v>
       </c>
       <c r="I40">
-        <v>1.8353691332888421E-9</v>
+        <v>1.258536568889377E-2</v>
       </c>
       <c r="J40">
-        <v>1.7586827408632951E-9</v>
+        <v>1.2059517087360369E-2</v>
       </c>
       <c r="K40">
-        <v>1.685200501039306E-9</v>
+        <v>1.15556397784036E-2</v>
       </c>
       <c r="L40">
-        <v>1.61478853616832E-9</v>
+        <v>1.1072815745514379E-2</v>
       </c>
       <c r="M40">
-        <v>1.5473185623505851E-9</v>
+        <v>1.061016532924923E-2</v>
       </c>
       <c r="N40">
-        <v>1.482667655714097E-9</v>
+        <v>1.0166845624574501E-2</v>
       </c>
       <c r="O40">
-        <v>1.4207180284589991E-9</v>
+        <v>9.7420489451735641E-3</v>
       </c>
       <c r="P40">
-        <v>1.3613568142594199E-9</v>
+        <v>9.3350013519192671E-3</v>
       </c>
       <c r="Q40">
-        <v>1.3044758626317669E-9</v>
+        <v>8.9449612428304168E-3</v>
       </c>
       <c r="R40">
-        <v>1.249971541894839E-9</v>
+        <v>8.5712180019436018E-3</v>
       </c>
       <c r="S40">
-        <v>1.197744550362762E-9</v>
+        <v>8.2130907046384944E-3</v>
       </c>
       <c r="T40">
-        <v>1.1476997354267661E-9</v>
+        <v>7.869926877057988E-3</v>
       </c>
       <c r="U40">
-        <v>1.099745920196192E-9</v>
+        <v>7.5411013073629352E-3</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>0.45783180749955388</v>
-      </c>
-      <c r="B41" s="1">
-        <v>8.2451102462884674E-10</v>
+        <v>0.46058070866141648</v>
+      </c>
+      <c r="B41">
+        <v>1.1311651961044399E-2</v>
       </c>
       <c r="C41">
-        <v>7.9006085607851494E-10</v>
+        <v>1.083902235998347E-2</v>
       </c>
       <c r="D41">
-        <v>7.5705010322754348E-10</v>
+        <v>1.038614042624543E-2</v>
       </c>
       <c r="E41">
-        <v>7.2541862362546647E-10</v>
+        <v>9.952181052042236E-3</v>
       </c>
       <c r="F41">
-        <v>6.9510878772642985E-10</v>
+        <v>9.5363536046886872E-3</v>
       </c>
       <c r="G41">
-        <v>6.66065373893641E-10</v>
+        <v>9.1379004861449099E-3</v>
       </c>
       <c r="H41">
-        <v>6.3823546779080277E-10</v>
+        <v>8.7560957527448198E-3</v>
       </c>
       <c r="I41">
-        <v>6.1156836597722729E-10</v>
+        <v>8.3902437925958469E-3</v>
       </c>
       <c r="J41">
-        <v>5.8601548353099129E-10</v>
+        <v>8.039678058240244E-3</v>
       </c>
       <c r="K41">
-        <v>5.6153026553183284E-10</v>
+        <v>7.7037598522690653E-3</v>
       </c>
       <c r="L41">
-        <v>5.380681022425158E-10</v>
+        <v>7.3818771636762516E-3</v>
       </c>
       <c r="M41">
-        <v>5.1558624783413357E-10</v>
+        <v>7.0734435528328216E-3</v>
       </c>
       <c r="N41">
-        <v>4.9404374250727677E-10</v>
+        <v>6.7778970830496658E-3</v>
       </c>
       <c r="O41">
-        <v>4.7340133786717632E-10</v>
+        <v>6.4946992967823761E-3</v>
       </c>
       <c r="P41">
-        <v>4.5362142541686312E-10</v>
+        <v>6.2233342346128444E-3</v>
       </c>
       <c r="Q41">
-        <v>4.3466796803806409E-10</v>
+        <v>5.9633074952202773E-3</v>
       </c>
       <c r="R41">
-        <v>4.1650643433500379E-10</v>
+        <v>5.7141453346290678E-3</v>
       </c>
       <c r="S41">
-        <v>3.991037357214861E-10</v>
+        <v>5.475393803092329E-3</v>
       </c>
       <c r="T41">
-        <v>3.8242816613663848E-10</v>
+        <v>5.2466179180386584E-3</v>
       </c>
       <c r="U41">
-        <v>3.6644934427948752E-10</v>
+        <v>5.0274008715752907E-3</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>0.47203661311773198</v>
-      </c>
-      <c r="B42" s="1">
-        <v>1.649618880294288E-9</v>
+        <v>0.47749999999999942</v>
+      </c>
+      <c r="B42">
+        <v>1.6967477941566601E-2</v>
       </c>
       <c r="C42">
-        <v>1.580693606074298E-9</v>
+        <v>1.6258533539975209E-2</v>
       </c>
       <c r="D42">
-        <v>1.5146482051893271E-9</v>
+        <v>1.557921063936815E-2</v>
       </c>
       <c r="E42">
-        <v>1.451362349203691E-9</v>
+        <v>1.4928271578063351E-2</v>
       </c>
       <c r="F42">
-        <v>1.3907207373099271E-9</v>
+        <v>1.430453040703303E-2</v>
       </c>
       <c r="G42">
-        <v>1.332612886261682E-9</v>
+        <v>1.370685072921737E-2</v>
       </c>
       <c r="H42">
-        <v>1.27693292908376E-9</v>
+        <v>1.313414362911723E-2</v>
       </c>
       <c r="I42">
-        <v>1.223579422192561E-9</v>
+        <v>1.258536568889377E-2</v>
       </c>
       <c r="J42">
-        <v>1.17245516057553E-9</v>
+        <v>1.2059517087360369E-2</v>
       </c>
       <c r="K42">
-        <v>1.123467000692871E-9</v>
+        <v>1.15556397784036E-2</v>
       </c>
       <c r="L42">
-        <v>1.0765256907788799E-9</v>
+        <v>1.1072815745514379E-2</v>
       </c>
       <c r="M42">
-        <v>1.031545708233723E-9</v>
+        <v>1.061016532924923E-2</v>
       </c>
       <c r="N42">
-        <v>9.8844510380939763E-10</v>
+        <v>1.0166845624574501E-2</v>
       </c>
       <c r="O42">
-        <v>9.4714535230599896E-10</v>
+        <v>9.7420489451735641E-3</v>
       </c>
       <c r="P42">
-        <v>9.0757120950628E-10</v>
+        <v>9.3350013519192671E-3</v>
       </c>
       <c r="Q42">
-        <v>8.6965057508784469E-10</v>
+        <v>8.9449612428304168E-3</v>
       </c>
       <c r="R42">
-        <v>8.3331436126322605E-10</v>
+        <v>8.5712180019436018E-3</v>
       </c>
       <c r="S42">
-        <v>7.9849636690850774E-10</v>
+        <v>8.2130907046384944E-3</v>
       </c>
       <c r="T42">
-        <v>7.6513315695117753E-10</v>
+        <v>7.869926877057988E-3</v>
       </c>
       <c r="U42">
-        <v>7.3316394679746148E-10</v>
+        <v>7.5411013073629352E-3</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>0.49498283747181993</v>
-      </c>
-      <c r="B43" s="1">
-        <v>3.299226708161972E-9</v>
+        <v>0.49441929133858242</v>
+      </c>
+      <c r="B43">
+        <v>2.2623303922088889E-2</v>
       </c>
       <c r="C43">
-        <v>3.1613766215204989E-9</v>
+        <v>2.1678044719967031E-2</v>
       </c>
       <c r="D43">
-        <v>3.029286262253945E-9</v>
+        <v>2.077228085249095E-2</v>
       </c>
       <c r="E43">
-        <v>2.902714974297146E-9</v>
+        <v>1.9904362104084548E-2</v>
       </c>
       <c r="F43">
-        <v>2.7814321568076859E-9</v>
+        <v>1.9072707209377451E-2</v>
       </c>
       <c r="G43">
-        <v>2.6652168440330982E-9</v>
+        <v>1.8275800972289889E-2</v>
       </c>
       <c r="H43">
-        <v>2.5538573027322951E-9</v>
+        <v>1.7512191505489709E-2</v>
       </c>
       <c r="I43">
-        <v>2.44715064641775E-9</v>
+        <v>1.678048758519176E-2</v>
       </c>
       <c r="J43">
-        <v>2.3449024657156251E-9</v>
+        <v>1.607935611648055E-2</v>
       </c>
       <c r="K43">
-        <v>2.2469264741703862E-9</v>
+        <v>1.540751970453819E-2</v>
       </c>
       <c r="L43">
-        <v>2.1530441688486151E-9</v>
+        <v>1.4763754327352571E-2</v>
       </c>
       <c r="M43">
-        <v>2.063084505123642E-9</v>
+        <v>1.41468871056657E-2</v>
       </c>
       <c r="N43">
-        <v>1.9768835850485208E-9</v>
+        <v>1.3555794166099391E-2</v>
       </c>
       <c r="O43">
-        <v>1.8942843587495599E-9</v>
+        <v>1.2989398593564801E-2</v>
       </c>
       <c r="P43">
-        <v>1.8151363382964019E-9</v>
+        <v>1.2446668469225739E-2</v>
       </c>
       <c r="Q43">
-        <v>1.739295323527324E-9</v>
+        <v>1.19266149904406E-2</v>
       </c>
       <c r="R43">
-        <v>1.666623139330281E-9</v>
+        <v>1.1428290669258181E-2</v>
       </c>
       <c r="S43">
-        <v>1.5969873839009871E-9</v>
+        <v>1.09507876061847E-2</v>
       </c>
       <c r="T43">
-        <v>1.5302611875194309E-9</v>
+        <v>1.049323583607736E-2</v>
       </c>
       <c r="U43">
-        <v>1.466322981405322E-9</v>
+        <v>1.005480174315062E-2</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>0.51137299674002945</v>
-      </c>
-      <c r="B44" s="1">
-        <v>7.4232739088976917E-9</v>
+        <v>0.51321850393700708</v>
+      </c>
+      <c r="B44">
+        <v>6.2214085785744368E-2</v>
       </c>
       <c r="C44">
-        <v>7.1131106367062466E-9</v>
+        <v>5.961462297990925E-2</v>
       </c>
       <c r="D44">
-        <v>6.8159067752272622E-9</v>
+        <v>5.7123772344350038E-2</v>
       </c>
       <c r="E44">
-        <v>6.5311208473063744E-9</v>
+        <v>5.4736995786232451E-2</v>
       </c>
       <c r="F44">
-        <v>6.2582340000825028E-9</v>
+        <v>5.2449944825787922E-2</v>
       </c>
       <c r="G44">
-        <v>5.9967490596873042E-9</v>
+        <v>5.0258452673797152E-2</v>
       </c>
       <c r="H44">
-        <v>5.7461896254416949E-9</v>
+        <v>4.8158526640096649E-2</v>
       </c>
       <c r="I44">
-        <v>5.5060992018991554E-9</v>
+        <v>4.6146340859277289E-2</v>
       </c>
       <c r="J44">
-        <v>5.2760403671544521E-9</v>
+        <v>4.4218229320321462E-2</v>
       </c>
       <c r="K44">
-        <v>5.0555939759025632E-9</v>
+        <v>4.2370679187479977E-2</v>
       </c>
       <c r="L44">
-        <v>4.8443583957958152E-9</v>
+        <v>4.060032440021951E-2</v>
       </c>
       <c r="M44">
-        <v>4.6419487757079509E-9</v>
+        <v>3.8903939540580627E-2</v>
       </c>
       <c r="N44">
-        <v>4.4479963445720152E-9</v>
+        <v>3.7278433956773271E-2</v>
       </c>
       <c r="O44">
-        <v>4.262147739514558E-9</v>
+        <v>3.5720846132303169E-2</v>
       </c>
       <c r="P44">
-        <v>4.0840643620621018E-9</v>
+        <v>3.4228338290370738E-2</v>
       </c>
       <c r="Q44">
-        <v>3.9134217612469362E-9</v>
+        <v>3.2798191223711623E-2</v>
       </c>
       <c r="R44">
-        <v>3.7499090424883468E-9</v>
+        <v>3.1427799340459972E-2</v>
       </c>
       <c r="S44">
-        <v>3.5932283011722571E-9</v>
+        <v>3.0114665917007899E-2</v>
       </c>
       <c r="T44">
-        <v>3.4430940798973749E-9</v>
+        <v>2.8856398549212701E-2</v>
       </c>
       <c r="U44">
-        <v>3.299232848398975E-9</v>
+        <v>2.7650704793664171E-2</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>0.52557780235820739</v>
-      </c>
-      <c r="B45" s="1">
-        <v>1.402177153492805E-8</v>
+        <v>0.5235580708661417</v>
+      </c>
+      <c r="B45">
+        <v>0.1018048676494</v>
       </c>
       <c r="C45">
-        <v>1.343590624225963E-8</v>
+        <v>9.7551201239851573E-2</v>
       </c>
       <c r="D45">
-        <v>1.287451989223398E-8</v>
+        <v>9.3475263836209202E-2</v>
       </c>
       <c r="E45">
-        <v>1.2336589692341609E-8</v>
+        <v>8.9569629468380429E-2</v>
       </c>
       <c r="F45">
-        <v>1.1821135584946549E-8</v>
+        <v>8.5827182442198474E-2</v>
       </c>
       <c r="G45">
-        <v>1.132721846171457E-8</v>
+        <v>8.2241104375304463E-2</v>
       </c>
       <c r="H45">
-        <v>1.085393845264718E-8</v>
+        <v>7.8804861774703652E-2</v>
       </c>
       <c r="I45">
-        <v>1.040043328660414E-8</v>
+        <v>7.5512194133362881E-2</v>
       </c>
       <c r="J45">
-        <v>9.9658767203274442E-9</v>
+        <v>7.2357102524162442E-2</v>
       </c>
       <c r="K45">
-        <v>9.5494770331047573E-9</v>
+        <v>6.9333838670421824E-2</v>
       </c>
       <c r="L45">
-        <v>9.1504755843296261E-9</v>
+        <v>6.6436894473086511E-2</v>
       </c>
       <c r="M45">
-        <v>8.7681454313304529E-9</v>
+        <v>6.3660991975495629E-2</v>
       </c>
       <c r="N45">
-        <v>8.4017900049501571E-9</v>
+        <v>6.1001073747447197E-2</v>
       </c>
       <c r="O45">
-        <v>8.0507418404634298E-9</v>
+        <v>5.8452293671041593E-2</v>
       </c>
       <c r="P45">
-        <v>7.7143613615195379E-9</v>
+        <v>5.6010008111515797E-2</v>
       </c>
       <c r="Q45">
-        <v>7.3920357148950453E-9</v>
+        <v>5.3669767456982688E-2</v>
       </c>
       <c r="R45">
-        <v>7.0831776539335929E-9</v>
+        <v>5.1427308011661788E-2</v>
       </c>
       <c r="S45">
-        <v>6.787224468638344E-9</v>
+        <v>4.9278544227831143E-2</v>
       </c>
       <c r="T45">
-        <v>6.5036369604679334E-9</v>
+        <v>4.7219561262348088E-2</v>
       </c>
       <c r="U45">
-        <v>6.231898459968025E-9</v>
+        <v>4.5246607844177771E-2</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>0.53868993115136965</v>
-      </c>
-      <c r="B46" s="1">
-        <v>1.8145763473530751E-8</v>
+        <v>0.53483759842519663</v>
+      </c>
+      <c r="B46">
+        <v>0.1527073014740995</v>
       </c>
       <c r="C46">
-        <v>1.7387587304304898E-8</v>
+        <v>0.14632680185977701</v>
       </c>
       <c r="D46">
-        <v>1.6661089664583759E-8</v>
+        <v>0.14021289575431339</v>
       </c>
       <c r="E46">
-        <v>1.5964946944799661E-8</v>
+        <v>0.13435444420257031</v>
       </c>
       <c r="F46">
-        <v>1.5297890839160521E-8</v>
+        <v>0.12874077366329731</v>
       </c>
       <c r="G46">
-        <v>1.4658706034917441E-8</v>
+        <v>0.1233616565629564</v>
       </c>
       <c r="H46">
-        <v>1.4046227998180459E-8</v>
+        <v>0.11820729266205519</v>
       </c>
       <c r="I46">
-        <v>1.3459340852248691E-8</v>
+        <v>0.113268291200044</v>
       </c>
       <c r="J46">
-        <v>1.289697534458909E-8</v>
+        <v>0.1085356537862434</v>
       </c>
       <c r="K46">
-        <v>1.235810689876016E-8</v>
+        <v>0.1040007580056324</v>
       </c>
       <c r="L46">
-        <v>1.1841753747731099E-8</v>
+        <v>9.9655341709629475E-2</v>
       </c>
       <c r="M46">
-        <v>1.134697514519574E-8</v>
+        <v>9.5491487963243152E-2</v>
       </c>
       <c r="N46">
-        <v>1.087286965162228E-8</v>
+        <v>9.1501610621170529E-2</v>
       </c>
       <c r="O46">
-        <v>1.041857349191624E-8</v>
+        <v>8.7678440506562136E-2</v>
       </c>
       <c r="P46">
-        <v>9.9832589817044463E-9</v>
+        <v>8.4015012167273445E-2</v>
       </c>
       <c r="Q46">
-        <v>9.5661330193728318E-9</v>
+        <v>8.0504651185473786E-2</v>
       </c>
       <c r="R46">
-        <v>9.1664356411108044E-9</v>
+        <v>7.7140962017492459E-2</v>
       </c>
       <c r="S46">
-        <v>8.7834386363294722E-9</v>
+        <v>7.391781634174649E-2</v>
       </c>
       <c r="T46">
-        <v>8.4164442209312562E-9</v>
+        <v>7.0829341893521927E-2</v>
       </c>
       <c r="U46">
-        <v>8.0647837660136702E-9</v>
+        <v>6.7869911766266458E-2</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>0.55726544544820533</v>
-      </c>
-      <c r="B47" s="1">
-        <v>2.474428320441432E-8</v>
+        <v>0.54423720472440962</v>
+      </c>
+      <c r="B47">
+        <v>0.1866422573572325</v>
       </c>
       <c r="C47">
-        <v>2.3710404091114479E-8</v>
+        <v>0.1788438689397272</v>
       </c>
       <c r="D47">
-        <v>2.2719723077839901E-8</v>
+        <v>0.17137131703304961</v>
       </c>
       <c r="E47">
-        <v>2.1770435238055369E-8</v>
+        <v>0.16421098735869691</v>
       </c>
       <c r="F47">
-        <v>2.0860811059648901E-8</v>
+        <v>0.15734983447736331</v>
       </c>
       <c r="G47">
-        <v>1.998919329392523E-8</v>
+        <v>0.150775358021391</v>
       </c>
       <c r="H47">
-        <v>1.9153993936256399E-8</v>
+        <v>0.1444755799202895</v>
       </c>
       <c r="I47">
-        <v>1.8353691332888419E-8</v>
+        <v>0.13843902257783139</v>
       </c>
       <c r="J47">
-        <v>1.7586827408632948E-8</v>
+        <v>0.132654687960964</v>
       </c>
       <c r="K47">
-        <v>1.685200501039307E-8</v>
+        <v>0.12711203756243949</v>
       </c>
       <c r="L47">
-        <v>1.6147885361683201E-8</v>
+        <v>0.12180097320065809</v>
       </c>
       <c r="M47">
-        <v>1.5473185623505851E-8</v>
+        <v>0.1167118186217415</v>
       </c>
       <c r="N47">
-        <v>1.482667655714097E-8</v>
+        <v>0.1118353018703195</v>
       </c>
       <c r="O47">
-        <v>1.420718028458998E-8</v>
+        <v>0.1071625383969092</v>
       </c>
       <c r="P47">
-        <v>1.36135681425942E-8</v>
+        <v>0.1026850148711119</v>
       </c>
       <c r="Q47">
-        <v>1.3044758626317671E-8</v>
+        <v>9.8394573671134536E-2</v>
       </c>
       <c r="R47">
-        <v>1.249971541894839E-8</v>
+        <v>9.4283398021379583E-2</v>
       </c>
       <c r="S47">
-        <v>1.197744550362762E-8</v>
+        <v>9.0343997751023405E-2</v>
       </c>
       <c r="T47">
-        <v>1.147699735426766E-8</v>
+        <v>8.656919564763782E-2</v>
       </c>
       <c r="U47">
-        <v>1.099745920196192E-8</v>
+        <v>8.2952114380992259E-2</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>0.56819221921274143</v>
-      </c>
-      <c r="B48" s="1">
-        <v>3.0517849813604902E-8</v>
+        <v>0.56585629921259772</v>
+      </c>
+      <c r="B48">
+        <v>0.22057721324036639</v>
       </c>
       <c r="C48">
-        <v>2.924273639672164E-8</v>
+        <v>0.21136093601967831</v>
       </c>
       <c r="D48">
-        <v>2.802090046288017E-8</v>
+        <v>0.2025297383117865</v>
       </c>
       <c r="E48">
-        <v>2.6850115943276158E-8</v>
+        <v>0.19406753051482409</v>
       </c>
       <c r="F48">
-        <v>2.5728249779924139E-8</v>
+        <v>0.18595889529142989</v>
       </c>
       <c r="G48">
-        <v>2.4653258039428721E-8</v>
+        <v>0.17818905947982619</v>
       </c>
       <c r="H48">
-        <v>2.3623182189132529E-8</v>
+        <v>0.17074386717852449</v>
       </c>
       <c r="I48">
-        <v>2.263614552885603E-8</v>
+        <v>0.1636097539556195</v>
       </c>
       <c r="J48">
-        <v>2.1690349771728389E-8</v>
+        <v>0.15677372213568519</v>
       </c>
       <c r="K48">
-        <v>2.0784071767879911E-8</v>
+        <v>0.15022331711924719</v>
       </c>
       <c r="L48">
-        <v>1.9915660365026971E-8</v>
+        <v>0.14394660469168741</v>
       </c>
       <c r="M48">
-        <v>1.9083533400229639E-8</v>
+        <v>0.13793214928024039</v>
       </c>
       <c r="N48">
-        <v>1.828617481734138E-8</v>
+        <v>0.13216899311946889</v>
       </c>
       <c r="O48">
-        <v>1.752213190489904E-8</v>
+        <v>0.1266466362872567</v>
       </c>
       <c r="P48">
-        <v>1.679001264942075E-8</v>
+        <v>0.1213550175749508</v>
       </c>
       <c r="Q48">
-        <v>1.6088483199289839E-8</v>
+        <v>0.1162844961567957</v>
       </c>
       <c r="R48">
-        <v>1.5416265434604141E-8</v>
+        <v>0.11142583402526721</v>
       </c>
       <c r="S48">
-        <v>1.477213463856314E-8</v>
+        <v>0.1067701791603007</v>
       </c>
       <c r="T48">
-        <v>1.4154917266150471E-8</v>
+        <v>0.1023090494017541</v>
       </c>
       <c r="U48">
-        <v>1.356348880604662E-8</v>
+        <v>9.8034316995718435E-2</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>0.58895308853820327</v>
-      </c>
-      <c r="B49" s="1">
-        <v>3.4641952276473643E-8</v>
+        <v>0.57901574803149569</v>
+      </c>
+      <c r="B49">
+        <v>0.26016799510402189</v>
       </c>
       <c r="C49">
-        <v>3.3194523365047878E-8</v>
+        <v>0.24929751427962049</v>
       </c>
       <c r="D49">
-        <v>3.1807571716477028E-8</v>
+        <v>0.2388812298036456</v>
       </c>
       <c r="E49">
-        <v>3.0478570436836583E-8</v>
+        <v>0.22890016419697201</v>
       </c>
       <c r="F49">
-        <v>2.920509821225979E-8</v>
+        <v>0.2193361329078404</v>
       </c>
       <c r="G49">
-        <v>2.7984834897534261E-8</v>
+        <v>0.21017171118133349</v>
       </c>
       <c r="H49">
-        <v>2.6815557289018059E-8</v>
+        <v>0.2013902023131314</v>
       </c>
       <c r="I49">
-        <v>2.5695135074174301E-8</v>
+        <v>0.192975607229705</v>
       </c>
       <c r="J49">
-        <v>2.4621526950344399E-8</v>
+        <v>0.18491259533952609</v>
       </c>
       <c r="K49">
-        <v>2.359277690568887E-8</v>
+        <v>0.177186476602189</v>
       </c>
       <c r="L49">
-        <v>2.2607010655519901E-8</v>
+        <v>0.16978317476455429</v>
       </c>
       <c r="M49">
-        <v>2.1662432227532969E-8</v>
+        <v>0.16268920171515541</v>
       </c>
       <c r="N49">
-        <v>2.0757320689716259E-8</v>
+        <v>0.15589163291014271</v>
       </c>
       <c r="O49">
-        <v>1.9890027014976231E-8</v>
+        <v>0.1493780838259951</v>
       </c>
       <c r="P49">
-        <v>1.9058971076767251E-8</v>
+        <v>0.14313668739609581</v>
       </c>
       <c r="Q49">
-        <v>1.826263877025128E-8</v>
+        <v>0.1371560723900668</v>
       </c>
       <c r="R49">
-        <v>1.7499579253743069E-8</v>
+        <v>0.13142534269646891</v>
       </c>
       <c r="S49">
-        <v>1.6768402305414551E-8</v>
+        <v>0.12593405747112391</v>
       </c>
       <c r="T49">
-        <v>1.606777579044303E-8</v>
+        <v>0.1206722121148895</v>
       </c>
       <c r="U49">
-        <v>1.5396423233988289E-8</v>
+        <v>0.115630220046232</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>0.60206521733136542</v>
-      </c>
-      <c r="B50" s="1">
-        <v>3.7941212141915417E-8</v>
+        <v>0.60157480314960676</v>
+      </c>
+      <c r="B50">
+        <v>0.29410295098715489</v>
       </c>
       <c r="C50">
-        <v>3.635593175845267E-8</v>
+        <v>0.28181458135957071</v>
       </c>
       <c r="D50">
-        <v>3.48368884231051E-8</v>
+        <v>0.2700396510823817</v>
       </c>
       <c r="E50">
-        <v>3.3381314583464432E-8</v>
+        <v>0.25875670735309858</v>
       </c>
       <c r="F50">
-        <v>3.1986558322503982E-8</v>
+        <v>0.24794519372190629</v>
       </c>
       <c r="G50">
-        <v>3.0650078527038159E-8</v>
+        <v>0.2375854126397681</v>
       </c>
       <c r="H50">
-        <v>2.936944025805603E-8</v>
+        <v>0.2276584895713657</v>
       </c>
       <c r="I50">
-        <v>2.8142310314494169E-8</v>
+        <v>0.21814633860749241</v>
       </c>
       <c r="J50">
-        <v>2.6966452982366329E-8</v>
+        <v>0.2090316295142467</v>
       </c>
       <c r="K50">
-        <v>2.5839725961505321E-8</v>
+        <v>0.20029775615899609</v>
       </c>
       <c r="L50">
-        <v>2.476007646249595E-8</v>
+        <v>0.1919288062555829</v>
       </c>
       <c r="M50">
-        <v>2.372553746668803E-8</v>
+        <v>0.18390953237365371</v>
       </c>
       <c r="N50">
-        <v>2.2734224142475599E-8</v>
+        <v>0.1762253241592916</v>
       </c>
       <c r="O50">
-        <v>2.1784330411313099E-8</v>
+        <v>0.1688621817163421</v>
       </c>
       <c r="P50">
-        <v>2.0874125657212122E-8</v>
+        <v>0.1618066900999342</v>
       </c>
       <c r="Q50">
-        <v>2.0001951573723698E-8</v>
+        <v>0.15504599487572751</v>
       </c>
       <c r="R50">
-        <v>1.916621914266186E-8</v>
+        <v>0.14856777870035601</v>
       </c>
       <c r="S50">
-        <v>1.8365405739063619E-8</v>
+        <v>0.14236023888040081</v>
       </c>
       <c r="T50">
-        <v>1.7598052357111241E-8</v>
+        <v>0.13641206586900539</v>
       </c>
       <c r="U50">
-        <v>1.6862760951962409E-8</v>
+        <v>0.13071242266095781</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>0.6206407316282011</v>
-      </c>
-      <c r="B51" s="1">
-        <v>3.7941212141915417E-8</v>
+        <v>0.6147342519685034</v>
+      </c>
+      <c r="B51">
+        <v>0.29410295098715489</v>
       </c>
       <c r="C51">
-        <v>3.635593175845267E-8</v>
+        <v>0.28181458135957071</v>
       </c>
       <c r="D51">
-        <v>3.48368884231051E-8</v>
+        <v>0.2700396510823817</v>
       </c>
       <c r="E51">
-        <v>3.3381314583464432E-8</v>
+        <v>0.25875670735309858</v>
       </c>
       <c r="F51">
-        <v>3.1986558322503982E-8</v>
+        <v>0.24794519372190629</v>
       </c>
       <c r="G51">
-        <v>3.0650078527038159E-8</v>
+        <v>0.2375854126397681</v>
       </c>
       <c r="H51">
-        <v>2.936944025805603E-8</v>
+        <v>0.2276584895713657</v>
       </c>
       <c r="I51">
-        <v>2.8142310314494169E-8</v>
+        <v>0.21814633860749241</v>
       </c>
       <c r="J51">
-        <v>2.6966452982366329E-8</v>
+        <v>0.2090316295142467</v>
       </c>
       <c r="K51">
-        <v>2.5839725961505321E-8</v>
+        <v>0.20029775615899609</v>
       </c>
       <c r="L51">
-        <v>2.476007646249595E-8</v>
+        <v>0.1919288062555829</v>
       </c>
       <c r="M51">
-        <v>2.372553746668803E-8</v>
+        <v>0.18390953237365371</v>
       </c>
       <c r="N51">
-        <v>2.2734224142475599E-8</v>
+        <v>0.1762253241592916</v>
       </c>
       <c r="O51">
-        <v>2.1784330411313099E-8</v>
+        <v>0.1688621817163421</v>
       </c>
       <c r="P51">
-        <v>2.0874125657212122E-8</v>
+        <v>0.1618066900999342</v>
       </c>
       <c r="Q51">
-        <v>2.0001951573723698E-8</v>
+        <v>0.15504599487572751</v>
       </c>
       <c r="R51">
-        <v>1.916621914266186E-8</v>
+        <v>0.14856777870035601</v>
       </c>
       <c r="S51">
-        <v>1.8365405739063619E-8</v>
+        <v>0.14236023888040081</v>
       </c>
       <c r="T51">
-        <v>1.7598052357111241E-8</v>
+        <v>0.13641206586900539</v>
       </c>
       <c r="U51">
-        <v>1.6862760951962409E-8</v>
+        <v>0.13071242266095781</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>0.64140160095366294</v>
-      </c>
-      <c r="B52" s="1">
-        <v>3.6291526947061509E-8</v>
+        <v>0.63165354330708634</v>
+      </c>
+      <c r="B52">
+        <v>0.28844712500663328</v>
       </c>
       <c r="C52">
-        <v>3.477517460860979E-8</v>
+        <v>0.27639507017957959</v>
       </c>
       <c r="D52">
-        <v>3.3322179329167518E-8</v>
+        <v>0.26484658086925961</v>
       </c>
       <c r="E52">
-        <v>3.1929893889599322E-8</v>
+        <v>0.25378061682707798</v>
       </c>
       <c r="F52">
-        <v>3.0595781678321048E-8</v>
+        <v>0.24317701691956251</v>
       </c>
       <c r="G52">
-        <v>2.9317412069834881E-8</v>
+        <v>0.23301646239669621</v>
       </c>
       <c r="H52">
-        <v>2.8092455996360919E-8</v>
+        <v>0.22328044169499381</v>
       </c>
       <c r="I52">
-        <v>2.6918681704497372E-8</v>
+        <v>0.21395121671119491</v>
       </c>
       <c r="J52">
-        <v>2.579395068917818E-8</v>
+        <v>0.20501179048512699</v>
       </c>
       <c r="K52">
-        <v>2.4716213797520321E-8</v>
+        <v>0.19644587623286189</v>
       </c>
       <c r="L52">
-        <v>2.3683507495462199E-8</v>
+        <v>0.1882378676737452</v>
       </c>
       <c r="M52">
-        <v>2.269395029039148E-8</v>
+        <v>0.1803728105972377</v>
       </c>
       <c r="N52">
-        <v>2.1745739303244559E-8</v>
+        <v>0.17283637561776721</v>
       </c>
       <c r="O52">
-        <v>2.0837146983832471E-8</v>
+        <v>0.1656148320679513</v>
       </c>
       <c r="P52">
-        <v>1.9966517963408889E-8</v>
+        <v>0.15869502298262819</v>
       </c>
       <c r="Q52">
-        <v>1.913226603874566E-8</v>
+        <v>0.1520643411281177</v>
       </c>
       <c r="R52">
-        <v>1.8332871282221609E-8</v>
+        <v>0.14571070603304179</v>
       </c>
       <c r="S52">
-        <v>1.7566877272658941E-8</v>
+        <v>0.13962254197885501</v>
       </c>
       <c r="T52">
-        <v>1.6832888441862509E-8</v>
+        <v>0.13378875690998629</v>
       </c>
       <c r="U52">
-        <v>1.612956753202734E-8</v>
+        <v>0.1281987222251704</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>0.6545137297468252</v>
-      </c>
-      <c r="B53" s="1">
-        <v>3.4641952276473643E-8</v>
+        <v>0.64481299212598431</v>
+      </c>
+      <c r="B53">
+        <v>0.25451216912349939</v>
       </c>
       <c r="C53">
-        <v>3.3194523365047878E-8</v>
+        <v>0.24387800309962851</v>
       </c>
       <c r="D53">
-        <v>3.1807571716477028E-8</v>
+        <v>0.23368815959052261</v>
       </c>
       <c r="E53">
-        <v>3.0478570436836583E-8</v>
+        <v>0.22392407367095071</v>
       </c>
       <c r="F53">
-        <v>2.920509821225979E-8</v>
+        <v>0.21456795610549581</v>
       </c>
       <c r="G53">
-        <v>2.7984834897534261E-8</v>
+        <v>0.2056027609382608</v>
       </c>
       <c r="H53">
-        <v>2.6815557289018059E-8</v>
+        <v>0.19701215443675879</v>
       </c>
       <c r="I53">
-        <v>2.5695135074174301E-8</v>
+        <v>0.18878048533340691</v>
       </c>
       <c r="J53">
-        <v>2.4621526950344399E-8</v>
+        <v>0.1808927563104058</v>
       </c>
       <c r="K53">
-        <v>2.359277690568887E-8</v>
+        <v>0.1733345966760543</v>
       </c>
       <c r="L53">
-        <v>2.2607010655519901E-8</v>
+        <v>0.16609223618271601</v>
       </c>
       <c r="M53">
-        <v>2.1662432227532969E-8</v>
+        <v>0.15915247993873879</v>
       </c>
       <c r="N53">
-        <v>2.0757320689716259E-8</v>
+        <v>0.15250268436861769</v>
       </c>
       <c r="O53">
-        <v>1.9890027014976231E-8</v>
+        <v>0.14613073417760369</v>
       </c>
       <c r="P53">
-        <v>1.9058971076767251E-8</v>
+        <v>0.14002502027878919</v>
       </c>
       <c r="Q53">
-        <v>1.826263877025128E-8</v>
+        <v>0.13417441864245649</v>
       </c>
       <c r="R53">
-        <v>1.7499579253743069E-8</v>
+        <v>0.12856827002915419</v>
       </c>
       <c r="S53">
-        <v>1.6768402305414551E-8</v>
+        <v>0.1231963605695776</v>
       </c>
       <c r="T53">
-        <v>1.606777579044303E-8</v>
+        <v>0.11804890315586999</v>
       </c>
       <c r="U53">
-        <v>1.5396423233988289E-8</v>
+        <v>0.11311651961044419</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>0.67527459907228693</v>
-      </c>
-      <c r="B54" s="1">
-        <v>2.969311774044398E-8</v>
+        <v>0.6589124015748038</v>
+      </c>
+      <c r="B54">
+        <v>0.26016799510402189</v>
       </c>
       <c r="C54">
-        <v>2.845246372808118E-8</v>
+        <v>0.24929751427962049</v>
       </c>
       <c r="D54">
-        <v>2.7263647397158461E-8</v>
+        <v>0.2388812298036456</v>
       </c>
       <c r="E54">
-        <v>2.6124502837445971E-8</v>
+        <v>0.22890016419697201</v>
       </c>
       <c r="F54">
-        <v>2.503295463595435E-8</v>
+        <v>0.2193361329078404</v>
       </c>
       <c r="G54">
-        <v>2.3987014095729741E-8</v>
+        <v>0.21017171118133349</v>
       </c>
       <c r="H54">
-        <v>2.298477561263723E-8</v>
+        <v>0.2013902023131314</v>
       </c>
       <c r="I54">
-        <v>2.2024413203531358E-8</v>
+        <v>0.192975607229705</v>
       </c>
       <c r="J54">
-        <v>2.1104177179488679E-8</v>
+        <v>0.18491259533952609</v>
       </c>
       <c r="K54">
-        <v>2.0222390958040969E-8</v>
+        <v>0.177186476602189</v>
       </c>
       <c r="L54">
-        <v>1.9377448008601549E-8</v>
+        <v>0.16978317476455429</v>
       </c>
       <c r="M54">
-        <v>1.856780892551941E-8</v>
+        <v>0.16268920171515541</v>
       </c>
       <c r="N54">
-        <v>1.7791998623428611E-8</v>
+        <v>0.15589163291014271</v>
       </c>
       <c r="O54">
-        <v>1.7048603649783109E-8</v>
+        <v>0.1493780838259951</v>
       </c>
       <c r="P54">
-        <v>1.6336269609680721E-8</v>
+        <v>0.14313668739609581</v>
       </c>
       <c r="Q54">
-        <v>1.5653698698284471E-8</v>
+        <v>0.1371560723900668</v>
       </c>
       <c r="R54">
-        <v>1.4999647336345731E-8</v>
+        <v>0.13142534269646891</v>
       </c>
       <c r="S54">
-        <v>1.4372923904521079E-8</v>
+        <v>0.12593405747112391</v>
       </c>
       <c r="T54">
-        <v>1.3772386572355349E-8</v>
+        <v>0.1206722121148895</v>
       </c>
       <c r="U54">
-        <v>1.31969412179751E-8</v>
+        <v>0.115630220046232</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>0.68620137283682303</v>
-      </c>
-      <c r="B55" s="1">
-        <v>2.5569015277575242E-8</v>
+        <v>0.6739517716535437</v>
+      </c>
+      <c r="B55">
+        <v>0.2092655612793215</v>
       </c>
       <c r="C55">
-        <v>2.4500676759754938E-8</v>
+        <v>0.2005219136596943</v>
       </c>
       <c r="D55">
-        <v>2.3476976143561601E-8</v>
+        <v>0.19214359788554061</v>
       </c>
       <c r="E55">
-        <v>2.249604834388556E-8</v>
+        <v>0.18411534946278149</v>
       </c>
       <c r="F55">
-        <v>2.1556106203618689E-8</v>
+        <v>0.17642254168674079</v>
       </c>
       <c r="G55">
-        <v>2.065543723762421E-8</v>
+        <v>0.16905115899368089</v>
       </c>
       <c r="H55">
-        <v>1.97924005127517E-8</v>
+        <v>0.16198777142577919</v>
       </c>
       <c r="I55">
-        <v>1.8965423658213091E-8</v>
+        <v>0.15521951016302321</v>
       </c>
       <c r="J55">
-        <v>1.8173000000872669E-8</v>
+        <v>0.14873404407744459</v>
       </c>
       <c r="K55">
-        <v>1.7413685820232009E-8</v>
+        <v>0.14251955726697779</v>
       </c>
       <c r="L55">
-        <v>1.6686097718108619E-8</v>
+        <v>0.13656472752801069</v>
       </c>
       <c r="M55">
-        <v>1.598891009821608E-8</v>
+        <v>0.13085870572740729</v>
       </c>
       <c r="N55">
-        <v>1.5320852751053739E-8</v>
+        <v>0.1253910960364189</v>
       </c>
       <c r="O55">
-        <v>1.4680708539705921E-8</v>
+        <v>0.120151936990474</v>
       </c>
       <c r="P55">
-        <v>1.4067311182334231E-8</v>
+        <v>0.1151316833403377</v>
       </c>
       <c r="Q55">
-        <v>1.347954312732304E-8</v>
+        <v>0.1103211886615752</v>
       </c>
       <c r="R55">
-        <v>1.2916333517206809E-8</v>
+        <v>0.1057116886906378</v>
       </c>
       <c r="S55">
-        <v>1.237665623766967E-8</v>
+        <v>0.10129478535720809</v>
       </c>
       <c r="T55">
-        <v>1.185952804806278E-8</v>
+        <v>9.7062431483715239E-2</v>
       </c>
       <c r="U55">
-        <v>1.136400679003344E-8</v>
+        <v>9.3006916124142927E-2</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>0.69822082342637493</v>
-      </c>
-      <c r="B56" s="1">
-        <v>2.0620180741545581E-8</v>
+        <v>0.68899114173228349</v>
+      </c>
+      <c r="B56">
+        <v>0.192298083337755</v>
       </c>
       <c r="C56">
-        <v>1.9758617122788241E-8</v>
+        <v>0.18426338011971921</v>
       </c>
       <c r="D56">
-        <v>1.8933051824243041E-8</v>
+        <v>0.17656438724617249</v>
       </c>
       <c r="E56">
-        <v>1.8141980744494958E-8</v>
+        <v>0.16918707788471821</v>
       </c>
       <c r="F56">
-        <v>1.7383962627313249E-8</v>
+        <v>0.16211801127970779</v>
       </c>
       <c r="G56">
-        <v>1.6657616435819699E-8</v>
+        <v>0.1553443082644636</v>
       </c>
       <c r="H56">
-        <v>1.5961618836370869E-8</v>
+        <v>0.14885362779666211</v>
       </c>
       <c r="I56">
-        <v>1.5294701787570159E-8</v>
+        <v>0.1426341444741295</v>
       </c>
       <c r="J56">
-        <v>1.465565023001695E-8</v>
+        <v>0.13667452699008431</v>
       </c>
       <c r="K56">
-        <v>1.4043299872584109E-8</v>
+        <v>0.13096391748857419</v>
       </c>
       <c r="L56">
-        <v>1.345653507119027E-8</v>
+        <v>0.12549191178249641</v>
       </c>
       <c r="M56">
-        <v>1.289428679620252E-8</v>
+        <v>0.1202485403981581</v>
       </c>
       <c r="N56">
-        <v>1.23555306847661E-8</v>
+        <v>0.11522425041184441</v>
       </c>
       <c r="O56">
-        <v>1.1839285174512799E-8</v>
+        <v>0.1104098880453005</v>
       </c>
       <c r="P56">
-        <v>1.1344609715247709E-8</v>
+        <v>0.1057966819884185</v>
       </c>
       <c r="Q56">
-        <v>1.087060305535623E-8</v>
+        <v>0.1013762274187448</v>
       </c>
       <c r="R56">
-        <v>1.041640159980947E-8</v>
+        <v>9.7140470688694261E-2</v>
       </c>
       <c r="S56">
-        <v>9.9811778367762041E-9</v>
+        <v>9.3081694652569685E-2</v>
       </c>
       <c r="T56">
-        <v>9.5641388299750981E-9</v>
+        <v>8.91925046066573E-2</v>
       </c>
       <c r="U56">
-        <v>9.1645247740202608E-9</v>
+        <v>8.546581481678002E-2</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>0.72007437095544713</v>
-      </c>
-      <c r="B57" s="1">
-        <v>1.4846503608088971E-8</v>
+        <v>0.69839074803149648</v>
+      </c>
+      <c r="B57">
+        <v>0.169674779415666</v>
       </c>
       <c r="C57">
-        <v>1.42261789109001E-8</v>
+        <v>0.16258533539975209</v>
       </c>
       <c r="D57">
-        <v>1.363177295795569E-8</v>
+        <v>0.15579210639368149</v>
       </c>
       <c r="E57">
-        <v>1.30622027981718E-8</v>
+        <v>0.1492827157806336</v>
       </c>
       <c r="F57">
-        <v>1.2516430728916329E-8</v>
+        <v>0.14304530407033031</v>
       </c>
       <c r="G57">
-        <v>1.199346240541354E-8</v>
+        <v>0.13706850729217371</v>
       </c>
       <c r="H57">
-        <v>1.149234502914249E-8</v>
+        <v>0.13134143629117229</v>
       </c>
       <c r="I57">
-        <v>1.1012165611928821E-8</v>
+        <v>0.12585365688893771</v>
       </c>
       <c r="J57">
-        <v>1.055204931256716E-8</v>
+        <v>0.1205951708736037</v>
       </c>
       <c r="K57">
-        <v>1.01111578429437E-8</v>
+        <v>0.11555639778403599</v>
       </c>
       <c r="L57">
-        <v>9.6886879407550479E-9</v>
+        <v>0.11072815745514381</v>
       </c>
       <c r="M57">
-        <v>9.2838699060406805E-9</v>
+        <v>0.1061016532924923</v>
       </c>
       <c r="N57">
-        <v>8.8959661988629309E-9</v>
+        <v>0.101668456245745</v>
       </c>
       <c r="O57">
-        <v>8.524270095579364E-9</v>
+        <v>9.7420489451735662E-2</v>
       </c>
       <c r="P57">
-        <v>8.1681044012595687E-9</v>
+        <v>9.3350013519192671E-2</v>
       </c>
       <c r="Q57">
-        <v>7.8268202159004116E-9</v>
+        <v>8.9449612428304182E-2</v>
       </c>
       <c r="R57">
-        <v>7.49979575219201E-9</v>
+        <v>8.5712180019436021E-2</v>
       </c>
       <c r="S57">
-        <v>7.1864352026803997E-9</v>
+        <v>8.2130907046384941E-2</v>
       </c>
       <c r="T57">
-        <v>6.8861676542630532E-9</v>
+        <v>7.8699268770579894E-2</v>
       </c>
       <c r="U57">
-        <v>6.5984460480395444E-9</v>
+        <v>7.5411013073629365E-2</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>0.73427917657362518</v>
-      </c>
-      <c r="B58" s="1">
-        <v>1.072250061705966E-8</v>
+        <v>0.71249015748031475</v>
+      </c>
+      <c r="B58">
+        <v>0.1300839975520105</v>
       </c>
       <c r="C58">
-        <v>1.027448725822675E-8</v>
+        <v>0.1246487571398098</v>
       </c>
       <c r="D58">
-        <v>9.8451930374812064E-9</v>
+        <v>0.1194406149018224</v>
       </c>
       <c r="E58">
-        <v>9.43383582160352E-9</v>
+        <v>0.1144500820984856</v>
       </c>
       <c r="F58">
-        <v>9.0396661568901884E-9</v>
+        <v>0.1096680664539198</v>
       </c>
       <c r="G58">
-        <v>8.6619659037204011E-9</v>
+        <v>0.1050858555906664</v>
       </c>
       <c r="H58">
-        <v>8.3000469281739883E-9</v>
+        <v>0.10069510115656539</v>
       </c>
       <c r="I58">
-        <v>7.9532498483169037E-9</v>
+        <v>9.6487803614852166E-2</v>
       </c>
       <c r="J58">
-        <v>7.6209428328700755E-9</v>
+        <v>9.2456297669762738E-2</v>
       </c>
       <c r="K58">
-        <v>7.3025204500729502E-9</v>
+        <v>8.8593238301094196E-2</v>
       </c>
       <c r="L58">
-        <v>6.9974025646444294E-9</v>
+        <v>8.4891587382276854E-2</v>
       </c>
       <c r="M58">
-        <v>6.7050332808315916E-9</v>
+        <v>8.1344600857577415E-2</v>
       </c>
       <c r="N58">
-        <v>6.4248799296205356E-9</v>
+        <v>7.7945816455071107E-2</v>
       </c>
       <c r="O58">
-        <v>6.1564320982641171E-9</v>
+        <v>7.4689041912997287E-2</v>
       </c>
       <c r="P58">
-        <v>5.8992007003585016E-9</v>
+        <v>7.1568343698047668E-2</v>
       </c>
       <c r="Q58">
-        <v>5.6527170847742604E-9</v>
+        <v>6.8578036195033151E-2</v>
       </c>
       <c r="R58">
-        <v>5.4165321818186276E-9</v>
+        <v>6.5712671348234247E-2</v>
       </c>
       <c r="S58">
-        <v>5.1902156850732444E-9</v>
+        <v>6.2967028735561745E-2</v>
       </c>
       <c r="T58">
-        <v>4.9733552674168056E-9</v>
+        <v>6.0336106057444529E-2</v>
       </c>
       <c r="U58">
-        <v>4.765555829804297E-9</v>
+        <v>5.7815110023115797E-2</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>0.75394736769547643</v>
-      </c>
-      <c r="B59" s="1">
-        <v>9.0728927891919805E-9</v>
+        <v>0.72658956692913435</v>
+      </c>
+      <c r="B59">
+        <v>9.6149041668877486E-2</v>
       </c>
       <c r="C59">
-        <v>8.6938042427805442E-9</v>
+        <v>9.2131690059859592E-2</v>
       </c>
       <c r="D59">
-        <v>8.330554980416589E-9</v>
+        <v>8.8282193623086258E-2</v>
       </c>
       <c r="E59">
-        <v>7.9824831965100656E-9</v>
+        <v>8.4593538942359089E-2</v>
       </c>
       <c r="F59">
-        <v>7.6489547373924283E-9</v>
+        <v>8.1059005639853923E-2</v>
       </c>
       <c r="G59">
-        <v>7.3293619459489857E-9</v>
+        <v>7.7672154132231816E-2</v>
       </c>
       <c r="H59">
-        <v>7.0231225545254526E-9</v>
+        <v>7.4426813898331043E-2</v>
       </c>
       <c r="I59">
-        <v>6.7296786240917154E-9</v>
+        <v>7.1317072237064766E-2</v>
       </c>
       <c r="J59">
-        <v>6.4484955277299802E-9</v>
+        <v>6.8337263495042141E-2</v>
       </c>
       <c r="K59">
-        <v>6.179060976595434E-9</v>
+        <v>6.5481958744287125E-2</v>
       </c>
       <c r="L59">
-        <v>5.920884086574694E-9</v>
+        <v>6.274595589124822E-2</v>
       </c>
       <c r="M59">
-        <v>5.6734944839416717E-9</v>
+        <v>6.0124270199079052E-2</v>
       </c>
       <c r="N59">
-        <v>5.4364414483814126E-9</v>
+        <v>5.7612125205922217E-2</v>
       </c>
       <c r="O59">
-        <v>5.2092930918205573E-9</v>
+        <v>5.5204944022650249E-2</v>
       </c>
       <c r="P59">
-        <v>4.991635571568381E-9</v>
+        <v>5.2898340994209231E-2</v>
       </c>
       <c r="Q59">
-        <v>4.7830723363347807E-9</v>
+        <v>5.0688113709372408E-2</v>
       </c>
       <c r="R59">
-        <v>4.5832234037515723E-9</v>
+        <v>4.857023534434713E-2</v>
       </c>
       <c r="S59">
-        <v>4.3917246680807641E-9</v>
+        <v>4.6540847326284843E-2</v>
       </c>
       <c r="T59">
-        <v>4.2082272368485521E-9</v>
+        <v>4.459625230332865E-2</v>
       </c>
       <c r="U59">
-        <v>4.0323967951964373E-9</v>
+        <v>4.273290740839001E-2</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>0.77470823839953296</v>
-      </c>
-      <c r="B60" s="1">
-        <v>7.4232739088976917E-9</v>
+        <v>0.745388779527559</v>
+      </c>
+      <c r="B60">
+        <v>6.2214085785744368E-2</v>
       </c>
       <c r="C60">
-        <v>7.1131106367062466E-9</v>
+        <v>5.961462297990925E-2</v>
       </c>
       <c r="D60">
-        <v>6.8159067752272622E-9</v>
+        <v>5.7123772344350038E-2</v>
       </c>
       <c r="E60">
-        <v>6.5311208473063744E-9</v>
+        <v>5.4736995786232451E-2</v>
       </c>
       <c r="F60">
-        <v>6.2582340000825028E-9</v>
+        <v>5.2449944825787922E-2</v>
       </c>
       <c r="G60">
-        <v>5.9967490596873042E-9</v>
+        <v>5.0258452673797152E-2</v>
       </c>
       <c r="H60">
-        <v>5.7461896254416949E-9</v>
+        <v>4.8158526640096649E-2</v>
       </c>
       <c r="I60">
-        <v>5.5060992018991554E-9</v>
+        <v>4.6146340859277289E-2</v>
       </c>
       <c r="J60">
-        <v>5.2760403671544521E-9</v>
+        <v>4.4218229320321462E-2</v>
       </c>
       <c r="K60">
-        <v>5.0555939759025632E-9</v>
+        <v>4.2370679187479977E-2</v>
       </c>
       <c r="L60">
-        <v>4.8443583957958152E-9</v>
+        <v>4.060032440021951E-2</v>
       </c>
       <c r="M60">
-        <v>4.6419487757079509E-9</v>
+        <v>3.8903939540580627E-2</v>
       </c>
       <c r="N60">
-        <v>4.4479963445720152E-9</v>
+        <v>3.7278433956773271E-2</v>
       </c>
       <c r="O60">
-        <v>4.262147739514558E-9</v>
+        <v>3.5720846132303169E-2</v>
       </c>
       <c r="P60">
-        <v>4.0840643620621018E-9</v>
+        <v>3.4228338290370738E-2</v>
       </c>
       <c r="Q60">
-        <v>3.9134217612469362E-9</v>
+        <v>3.2798191223711623E-2</v>
       </c>
       <c r="R60">
-        <v>3.7499090424883468E-9</v>
+        <v>3.1427799340459972E-2</v>
       </c>
       <c r="S60">
-        <v>3.5932283011722571E-9</v>
+        <v>3.0114665917007899E-2</v>
       </c>
       <c r="T60">
-        <v>3.4430940798973749E-9</v>
+        <v>2.8856398549212701E-2</v>
       </c>
       <c r="U60">
-        <v>3.299232848398975E-9</v>
+        <v>2.7650704793664171E-2</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>0.79109839766774248</v>
-      </c>
-      <c r="B61" s="1">
-        <v>7.4232739088976917E-9</v>
+        <v>0.7604281496062989</v>
+      </c>
+      <c r="B61">
+        <v>6.7869911766266666E-2</v>
       </c>
       <c r="C61">
-        <v>7.1131106367062466E-9</v>
+        <v>6.5034134159901086E-2</v>
       </c>
       <c r="D61">
-        <v>6.8159067752272622E-9</v>
+        <v>6.2316842557472843E-2</v>
       </c>
       <c r="E61">
-        <v>6.5311208473063744E-9</v>
+        <v>5.9713086312253652E-2</v>
       </c>
       <c r="F61">
-        <v>6.2582340000825028E-9</v>
+        <v>5.7218121628132348E-2</v>
       </c>
       <c r="G61">
-        <v>5.9967490596873042E-9</v>
+        <v>5.4827402916869668E-2</v>
       </c>
       <c r="H61">
-        <v>5.7461896254416949E-9</v>
+        <v>5.2536574516469127E-2</v>
       </c>
       <c r="I61">
-        <v>5.5060992018991554E-9</v>
+        <v>5.0341462755575279E-2</v>
       </c>
       <c r="J61">
-        <v>5.2760403671544521E-9</v>
+        <v>4.8238068349441658E-2</v>
       </c>
       <c r="K61">
-        <v>5.0555939759025632E-9</v>
+        <v>4.6222559113614572E-2</v>
       </c>
       <c r="L61">
-        <v>4.8443583957958152E-9</v>
+        <v>4.4291262982057697E-2</v>
       </c>
       <c r="M61">
-        <v>4.6419487757079509E-9</v>
+        <v>4.24406613169971E-2</v>
       </c>
       <c r="N61">
-        <v>4.4479963445720152E-9</v>
+        <v>4.0667382498298148E-2</v>
       </c>
       <c r="O61">
-        <v>4.262147739514558E-9</v>
+        <v>3.8968195780694409E-2</v>
       </c>
       <c r="P61">
-        <v>4.0840643620621018E-9</v>
+        <v>3.7340005407677207E-2</v>
       </c>
       <c r="Q61">
-        <v>3.9134217612469362E-9</v>
+        <v>3.5779844971321813E-2</v>
       </c>
       <c r="R61">
-        <v>3.7499090424883468E-9</v>
+        <v>3.4284872007774553E-2</v>
       </c>
       <c r="S61">
-        <v>3.5932283011722571E-9</v>
+        <v>3.2852362818554103E-2</v>
       </c>
       <c r="T61">
-        <v>3.4430940798973749E-9</v>
+        <v>3.1479707508232077E-2</v>
       </c>
       <c r="U61">
-        <v>3.299232848398975E-9</v>
+        <v>3.0164405229451859E-2</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>0.79983981640365232</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1.154735426691322E-8</v>
+        <v>0.77170767716535504</v>
+      </c>
+      <c r="B62">
+        <v>6.2214085785744368E-2</v>
       </c>
       <c r="C62">
-        <v>1.106487642377628E-8</v>
+        <v>5.961462297990925E-2</v>
       </c>
       <c r="D62">
-        <v>1.06025577325747E-8</v>
+        <v>5.7123772344350038E-2</v>
       </c>
       <c r="E62">
-        <v>1.015955589264631E-8</v>
+        <v>5.4736995786232451E-2</v>
       </c>
       <c r="F62">
-        <v>9.7350637967938244E-9</v>
+        <v>5.2449944825787922E-2</v>
       </c>
       <c r="G62">
-        <v>9.3283080608123084E-9</v>
+        <v>5.0258452673797152E-2</v>
       </c>
       <c r="H62">
-        <v>8.9385476144567691E-9</v>
+        <v>4.8158526640096649E-2</v>
       </c>
       <c r="I62">
-        <v>8.5650723512826742E-9</v>
+        <v>4.6146340859277289E-2</v>
       </c>
       <c r="J62">
-        <v>8.2072018348995856E-9</v>
+        <v>4.4218229320321462E-2</v>
       </c>
       <c r="K62">
-        <v>7.8642840592808082E-9</v>
+        <v>4.2370679187479977E-2</v>
       </c>
       <c r="L62">
-        <v>7.53569426087045E-9</v>
+        <v>4.060032440021951E-2</v>
       </c>
       <c r="M62">
-        <v>7.2208337803236734E-9</v>
+        <v>3.8903939540580627E-2</v>
       </c>
       <c r="N62">
-        <v>6.919128971806335E-9</v>
+        <v>3.7278433956773271E-2</v>
       </c>
       <c r="O62">
-        <v>6.6300301578668691E-9</v>
+        <v>3.5720846132303169E-2</v>
       </c>
       <c r="P62">
-        <v>6.3530106279762756E-9</v>
+        <v>3.4228338290370738E-2</v>
       </c>
       <c r="Q62">
-        <v>6.0875656789116434E-9</v>
+        <v>3.2798191223711623E-2</v>
       </c>
       <c r="R62">
-        <v>5.833211695234924E-9</v>
+        <v>3.1427799340459972E-2</v>
       </c>
       <c r="S62">
-        <v>5.5894852681916113E-9</v>
+        <v>3.0114665917007899E-2</v>
       </c>
       <c r="T62">
-        <v>5.3559423514240906E-9</v>
+        <v>2.8856398549212701E-2</v>
       </c>
       <c r="U62">
-        <v>5.1321574519614336E-9</v>
+        <v>2.7650704793664171E-2</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>0.81076659016818853</v>
-      </c>
-      <c r="B63" s="1">
-        <v>1.072250061705966E-8</v>
+        <v>0.78392716535433127</v>
+      </c>
+      <c r="B63">
+        <v>6.7869911766266666E-2</v>
       </c>
       <c r="C63">
-        <v>1.027448725822675E-8</v>
+        <v>6.5034134159901086E-2</v>
       </c>
       <c r="D63">
-        <v>9.8451930374812064E-9</v>
+        <v>6.2316842557472843E-2</v>
       </c>
       <c r="E63">
-        <v>9.43383582160352E-9</v>
+        <v>5.9713086312253652E-2</v>
       </c>
       <c r="F63">
-        <v>9.0396661568901884E-9</v>
+        <v>5.7218121628132348E-2</v>
       </c>
       <c r="G63">
-        <v>8.6619659037204011E-9</v>
+        <v>5.4827402916869668E-2</v>
       </c>
       <c r="H63">
-        <v>8.3000469281739883E-9</v>
+        <v>5.2536574516469127E-2</v>
       </c>
       <c r="I63">
-        <v>7.9532498483169037E-9</v>
+        <v>5.0341462755575279E-2</v>
       </c>
       <c r="J63">
-        <v>7.6209428328700755E-9</v>
+        <v>4.8238068349441658E-2</v>
       </c>
       <c r="K63">
-        <v>7.3025204500729502E-9</v>
+        <v>4.6222559113614572E-2</v>
       </c>
       <c r="L63">
-        <v>6.9974025646444294E-9</v>
+        <v>4.4291262982057697E-2</v>
       </c>
       <c r="M63">
-        <v>6.7050332808315916E-9</v>
+        <v>4.24406613169971E-2</v>
       </c>
       <c r="N63">
-        <v>6.4248799296205356E-9</v>
+        <v>4.0667382498298148E-2</v>
       </c>
       <c r="O63">
-        <v>6.1564320982641171E-9</v>
+        <v>3.8968195780694409E-2</v>
       </c>
       <c r="P63">
-        <v>5.8992007003585016E-9</v>
+        <v>3.7340005407677207E-2</v>
       </c>
       <c r="Q63">
-        <v>5.6527170847742604E-9</v>
+        <v>3.5779844971321813E-2</v>
       </c>
       <c r="R63">
-        <v>5.4165321818186276E-9</v>
+        <v>3.4284872007774553E-2</v>
       </c>
       <c r="S63">
-        <v>5.1902156850732444E-9</v>
+        <v>3.2852362818554103E-2</v>
       </c>
       <c r="T63">
-        <v>4.9733552674168056E-9</v>
+        <v>3.1479707508232077E-2</v>
       </c>
       <c r="U63">
-        <v>4.765555829804297E-9</v>
+        <v>3.0164405229451859E-2</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>0.83043478266863457</v>
-      </c>
-      <c r="B64" s="1">
-        <v>8.2480833490448361E-9</v>
+        <v>0.80272637795275614</v>
+      </c>
+      <c r="B64">
+        <v>7.9181563727311069E-2</v>
       </c>
       <c r="C64">
-        <v>7.9034574397433946E-9</v>
+        <v>7.5873156519884549E-2</v>
       </c>
       <c r="D64">
-        <v>7.5732308778219248E-9</v>
+        <v>7.2702982983718273E-2</v>
       </c>
       <c r="E64">
-        <v>7.25680202190822E-9</v>
+        <v>6.9665267364295888E-2</v>
       </c>
       <c r="F64">
-        <v>6.9535943687374668E-9</v>
+        <v>6.6754475232821034E-2</v>
       </c>
       <c r="G64">
-        <v>6.6630555028181441E-9</v>
+        <v>6.3965303403014595E-2</v>
       </c>
       <c r="H64">
-        <v>6.3846560899835733E-9</v>
+        <v>6.129267026921395E-2</v>
       </c>
       <c r="I64">
-        <v>6.1178889129954342E-9</v>
+        <v>5.8731706548171128E-2</v>
       </c>
       <c r="J64">
-        <v>5.862267947442217E-9</v>
+        <v>5.6277746407681899E-2</v>
       </c>
       <c r="K64">
-        <v>5.6173274762489994E-9</v>
+        <v>5.3926318965883638E-2</v>
       </c>
       <c r="L64">
-        <v>5.3826212411852542E-9</v>
+        <v>5.1673140145733952E-2</v>
       </c>
       <c r="M64">
-        <v>5.1577216298248113E-9</v>
+        <v>4.9514104869829927E-2</v>
       </c>
       <c r="N64">
-        <v>4.9422188964767143E-9</v>
+        <v>4.7445279581347831E-2</v>
       </c>
       <c r="O64">
-        <v>4.7357204156675572E-9</v>
+        <v>4.5462895077476792E-2</v>
       </c>
       <c r="P64">
-        <v>4.537849966815241E-9</v>
+        <v>4.3563339642290061E-2</v>
       </c>
       <c r="Q64">
-        <v>4.3482470487908576E-9</v>
+        <v>4.1743152466542088E-2</v>
       </c>
       <c r="R64">
-        <v>4.1665662231199604E-9</v>
+        <v>3.9999017342403617E-2</v>
       </c>
       <c r="S64">
-        <v>3.9924764846265108E-9</v>
+        <v>3.832775662164644E-2</v>
       </c>
       <c r="T64">
-        <v>3.8256606583729637E-9</v>
+        <v>3.6726325426270738E-2</v>
       </c>
       <c r="U64">
-        <v>3.665814821797706E-9</v>
+        <v>3.5191806101027151E-2</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>0.85228832881911221</v>
-      </c>
-      <c r="B65" s="1">
-        <v>8.2480833490448361E-9</v>
+        <v>0.81682578740157441</v>
+      </c>
+      <c r="B65">
+        <v>7.3525737746788875E-2</v>
       </c>
       <c r="C65">
-        <v>7.9034574397433946E-9</v>
+        <v>7.0453645339892818E-2</v>
       </c>
       <c r="D65">
-        <v>7.5732308778219248E-9</v>
+        <v>6.7509912770595551E-2</v>
       </c>
       <c r="E65">
-        <v>7.25680202190822E-9</v>
+        <v>6.468917683827477E-2</v>
       </c>
       <c r="F65">
-        <v>6.9535943687374668E-9</v>
+        <v>6.1986298430476691E-2</v>
       </c>
       <c r="G65">
-        <v>6.6630555028181441E-9</v>
+        <v>5.9396353159942142E-2</v>
       </c>
       <c r="H65">
-        <v>6.3846560899835733E-9</v>
+        <v>5.6914622392841549E-2</v>
       </c>
       <c r="I65">
-        <v>6.1178889129954342E-9</v>
+        <v>5.4536584651873207E-2</v>
       </c>
       <c r="J65">
-        <v>5.862267947442217E-9</v>
+        <v>5.2257907378561778E-2</v>
       </c>
       <c r="K65">
-        <v>5.6173274762489994E-9</v>
+        <v>5.0074439039749112E-2</v>
       </c>
       <c r="L65">
-        <v>5.3826212411852542E-9</v>
+        <v>4.7982201563895821E-2</v>
       </c>
       <c r="M65">
-        <v>5.1577216298248113E-9</v>
+        <v>4.597738309341351E-2</v>
       </c>
       <c r="N65">
-        <v>4.9422188964767143E-9</v>
+        <v>4.4056331039822989E-2</v>
       </c>
       <c r="O65">
-        <v>4.7357204156675572E-9</v>
+        <v>4.2215545429085601E-2</v>
       </c>
       <c r="P65">
-        <v>4.537849966815241E-9</v>
+        <v>4.0451672524983627E-2</v>
       </c>
       <c r="Q65">
-        <v>4.3482470487908576E-9</v>
+        <v>3.8761498718931947E-2</v>
       </c>
       <c r="R65">
-        <v>4.1665662231199604E-9</v>
+        <v>3.7141944675089078E-2</v>
       </c>
       <c r="S65">
-        <v>3.9924764846265108E-9</v>
+        <v>3.5590059720100271E-2</v>
       </c>
       <c r="T65">
-        <v>3.8256606583729637E-9</v>
+        <v>3.4103016467251397E-2</v>
       </c>
       <c r="U65">
-        <v>3.665814821797706E-9</v>
+        <v>3.2678105665239508E-2</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>0.86540045761227447</v>
-      </c>
-      <c r="B66" s="1">
-        <v>8.2480833490448361E-9</v>
+        <v>0.83186515748031553</v>
+      </c>
+      <c r="B66">
+        <v>6.7869911766266666E-2</v>
       </c>
       <c r="C66">
-        <v>7.9034574397433946E-9</v>
+        <v>6.5034134159901086E-2</v>
       </c>
       <c r="D66">
-        <v>7.5732308778219248E-9</v>
+        <v>6.2316842557472843E-2</v>
       </c>
       <c r="E66">
-        <v>7.25680202190822E-9</v>
+        <v>5.9713086312253652E-2</v>
       </c>
       <c r="F66">
-        <v>6.9535943687374668E-9</v>
+        <v>5.7218121628132348E-2</v>
       </c>
       <c r="G66">
-        <v>6.6630555028181441E-9</v>
+        <v>5.4827402916869668E-2</v>
       </c>
       <c r="H66">
-        <v>6.3846560899835733E-9</v>
+        <v>5.2536574516469127E-2</v>
       </c>
       <c r="I66">
-        <v>6.1178889129954342E-9</v>
+        <v>5.0341462755575279E-2</v>
       </c>
       <c r="J66">
-        <v>5.862267947442217E-9</v>
+        <v>4.8238068349441658E-2</v>
       </c>
       <c r="K66">
-        <v>5.6173274762489994E-9</v>
+        <v>4.6222559113614572E-2</v>
       </c>
       <c r="L66">
-        <v>5.3826212411852542E-9</v>
+        <v>4.4291262982057697E-2</v>
       </c>
       <c r="M66">
-        <v>5.1577216298248113E-9</v>
+        <v>4.24406613169971E-2</v>
       </c>
       <c r="N66">
-        <v>4.9422188964767143E-9</v>
+        <v>4.0667382498298148E-2</v>
       </c>
       <c r="O66">
-        <v>4.7357204156675572E-9</v>
+        <v>3.8968195780694409E-2</v>
       </c>
       <c r="P66">
-        <v>4.537849966815241E-9</v>
+        <v>3.7340005407677207E-2</v>
       </c>
       <c r="Q66">
-        <v>4.3482470487908576E-9</v>
+        <v>3.5779844971321813E-2</v>
       </c>
       <c r="R66">
-        <v>4.1665662231199604E-9</v>
+        <v>3.4284872007774553E-2</v>
       </c>
       <c r="S66">
-        <v>3.9924764846265108E-9</v>
+        <v>3.2852362818554103E-2</v>
       </c>
       <c r="T66">
-        <v>3.8256606583729637E-9</v>
+        <v>3.1479707508232077E-2</v>
       </c>
       <c r="U66">
-        <v>3.665814821797706E-9</v>
+        <v>3.0164405229451859E-2</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>0.88288329508409435</v>
-      </c>
-      <c r="B67" s="1">
-        <v>6.5984644687505489E-9</v>
+        <v>0.85536417322834679</v>
+      </c>
+      <c r="B67">
+        <v>6.7869911766266666E-2</v>
       </c>
       <c r="C67">
-        <v>6.3227638336690962E-9</v>
+        <v>6.5034134159901086E-2</v>
       </c>
       <c r="D67">
-        <v>6.0585826726325988E-9</v>
+        <v>6.2316842557472843E-2</v>
       </c>
       <c r="E67">
-        <v>5.8054396727045288E-9</v>
+        <v>5.9713086312253652E-2</v>
       </c>
       <c r="F67">
-        <v>5.5628736314275397E-9</v>
+        <v>5.7218121628132348E-2</v>
       </c>
       <c r="G67">
-        <v>5.3304426165564634E-9</v>
+        <v>5.4827402916869668E-2</v>
       </c>
       <c r="H67">
-        <v>5.1077231608998139E-9</v>
+        <v>5.2536574516469127E-2</v>
       </c>
       <c r="I67">
-        <v>4.8943094908028717E-9</v>
+        <v>5.0341462755575279E-2</v>
       </c>
       <c r="J67">
-        <v>4.6898127868666863E-9</v>
+        <v>4.8238068349441658E-2</v>
       </c>
       <c r="K67">
-        <v>4.4938604755561286E-9</v>
+        <v>4.6222559113614572E-2</v>
       </c>
       <c r="L67">
-        <v>4.3060955504063736E-9</v>
+        <v>4.4291262982057697E-2</v>
       </c>
       <c r="M67">
-        <v>4.126175921591088E-9</v>
+        <v>4.24406613169971E-2</v>
       </c>
       <c r="N67">
-        <v>3.9537737926673161E-9</v>
+        <v>4.0667382498298148E-2</v>
       </c>
       <c r="O67">
-        <v>3.7885750633615579E-9</v>
+        <v>3.8968195780694409E-2</v>
       </c>
       <c r="P67">
-        <v>3.6302787573089621E-9</v>
+        <v>3.7340005407677207E-2</v>
       </c>
       <c r="Q67">
-        <v>3.478596473703014E-9</v>
+        <v>3.5779844971321813E-2</v>
       </c>
       <c r="R67">
-        <v>3.3332518618567341E-9</v>
+        <v>3.4284872007774553E-2</v>
       </c>
       <c r="S67">
-        <v>3.193980117718003E-9</v>
+        <v>3.2852362818554103E-2</v>
       </c>
       <c r="T67">
-        <v>3.0605275014217862E-9</v>
+        <v>3.1479707508232077E-2</v>
       </c>
       <c r="U67">
-        <v>2.9326508750002449E-9</v>
+        <v>3.0164405229451859E-2</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>0.90255148758454029</v>
-      </c>
-      <c r="B68" s="1">
-        <v>4.1240361483091156E-9</v>
+        <v>0.87792322834645653</v>
+      </c>
+      <c r="B68">
+        <v>5.655825980522218E-2</v>
       </c>
       <c r="C68">
-        <v>3.9517234245576481E-9</v>
+        <v>5.4195111799917518E-2</v>
       </c>
       <c r="D68">
-        <v>3.7866103648486076E-9</v>
+        <v>5.1930702131227323E-2</v>
       </c>
       <c r="E68">
-        <v>3.628396148898992E-9</v>
+        <v>4.9760905260211333E-2</v>
       </c>
       <c r="F68">
-        <v>3.4767925254626491E-9</v>
+        <v>4.7681768023443587E-2</v>
       </c>
       <c r="G68">
-        <v>3.331523287163939E-9</v>
+        <v>4.5689502430724699E-2</v>
       </c>
       <c r="H68">
-        <v>3.1923237672741748E-9</v>
+        <v>4.3780478763724241E-2</v>
       </c>
       <c r="I68">
-        <v>3.0589403575140308E-9</v>
+        <v>4.1951218962979368E-2</v>
       </c>
       <c r="J68">
-        <v>2.93113004600339E-9</v>
+        <v>4.0198390291201348E-2</v>
       </c>
       <c r="K68">
-        <v>2.808659974516822E-9</v>
+        <v>3.8518799261345452E-2</v>
       </c>
       <c r="L68">
-        <v>2.6913070142380541E-9</v>
+        <v>3.6909385818381379E-2</v>
       </c>
       <c r="M68">
-        <v>2.578857359240504E-9</v>
+        <v>3.5367217764164217E-2</v>
       </c>
       <c r="N68">
-        <v>2.4711061369532199E-9</v>
+        <v>3.3889485415248437E-2</v>
       </c>
       <c r="O68">
-        <v>2.36785703490256E-9</v>
+        <v>3.2473496483911977E-2</v>
       </c>
       <c r="P68">
-        <v>2.268921943049542E-9</v>
+        <v>3.1116671173064318E-2</v>
       </c>
       <c r="Q68">
-        <v>2.1741206110712468E-9</v>
+        <v>2.9816537476101478E-2</v>
       </c>
       <c r="R68">
-        <v>2.0832803199618951E-9</v>
+        <v>2.8570726673145429E-2</v>
       </c>
       <c r="S68">
-        <v>1.996235567355241E-9</v>
+        <v>2.737696901546173E-2</v>
       </c>
       <c r="T68">
-        <v>1.9128277659950199E-9</v>
+        <v>2.6233089590193371E-2</v>
       </c>
       <c r="U68">
-        <v>1.8329049548040521E-9</v>
+        <v>2.5137004357876531E-2</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>0.91784897002773413</v>
-      </c>
-      <c r="B69" s="1">
-        <v>8.2451102462884674E-10</v>
+        <v>0.89860236220472445</v>
+      </c>
+      <c r="B69">
+        <v>3.9590781863655493E-2</v>
       </c>
       <c r="C69">
-        <v>7.9006085607851494E-10</v>
+        <v>3.7936578259942233E-2</v>
       </c>
       <c r="D69">
-        <v>7.5705010322754348E-10</v>
+        <v>3.6351491491859088E-2</v>
       </c>
       <c r="E69">
-        <v>7.2541862362546647E-10</v>
+        <v>3.4832633682147909E-2</v>
       </c>
       <c r="F69">
-        <v>6.9510878772642985E-10</v>
+        <v>3.3377237616410482E-2</v>
       </c>
       <c r="G69">
-        <v>6.66065373893641E-10</v>
+        <v>3.1982651701507263E-2</v>
       </c>
       <c r="H69">
-        <v>6.3823546779080277E-10</v>
+        <v>3.064633513460694E-2</v>
       </c>
       <c r="I69">
-        <v>6.1156836597722729E-10</v>
+        <v>2.9365853274085529E-2</v>
       </c>
       <c r="J69">
-        <v>5.8601548353099129E-10</v>
+        <v>2.8138873203840922E-2</v>
       </c>
       <c r="K69">
-        <v>5.6153026553183284E-10</v>
+        <v>2.6963159482941791E-2</v>
       </c>
       <c r="L69">
-        <v>5.380681022425158E-10</v>
+        <v>2.5836570072866941E-2</v>
       </c>
       <c r="M69">
-        <v>5.1558624783413357E-10</v>
+        <v>2.4757052434914939E-2</v>
       </c>
       <c r="N69">
-        <v>4.9404374250727677E-10</v>
+        <v>2.3722639790673881E-2</v>
       </c>
       <c r="O69">
-        <v>4.7340133786717632E-10</v>
+        <v>2.2731447538738372E-2</v>
       </c>
       <c r="P69">
-        <v>4.5362142541686312E-10</v>
+        <v>2.1781669821144999E-2</v>
       </c>
       <c r="Q69">
-        <v>4.3466796803806409E-10</v>
+        <v>2.087157623327102E-2</v>
       </c>
       <c r="R69">
-        <v>4.1650643433500379E-10</v>
+        <v>1.9999508671201781E-2</v>
       </c>
       <c r="S69">
-        <v>3.991037357214861E-10</v>
+        <v>1.9163878310823199E-2</v>
       </c>
       <c r="T69">
-        <v>3.8242816613663848E-10</v>
+        <v>1.8363162713135341E-2</v>
       </c>
       <c r="U69">
-        <v>3.6644934427948752E-10</v>
+        <v>1.7595903050513551E-2</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>0.92986842061728592</v>
-      </c>
-      <c r="B70" s="1">
-        <v>-8.2451102462884674E-10</v>
+        <v>0.91270177165354394</v>
+      </c>
+      <c r="B70">
+        <v>5.6558259805222178E-3</v>
       </c>
       <c r="C70">
-        <v>-7.9006085607851494E-10</v>
+        <v>5.4195111799917517E-3</v>
       </c>
       <c r="D70">
-        <v>-7.5705010322754348E-10</v>
+        <v>5.1930702131227323E-3</v>
       </c>
       <c r="E70">
-        <v>-7.2541862362546647E-10</v>
+        <v>4.9760905260211336E-3</v>
       </c>
       <c r="F70">
-        <v>-6.9510878772642985E-10</v>
+        <v>4.7681768023443583E-3</v>
       </c>
       <c r="G70">
-        <v>-6.66065373893641E-10</v>
+        <v>4.5689502430724697E-3</v>
       </c>
       <c r="H70">
-        <v>-6.3823546779080277E-10</v>
+        <v>4.3780478763724238E-3</v>
       </c>
       <c r="I70">
-        <v>-6.1156836597722729E-10</v>
+        <v>4.1951218962979356E-3</v>
       </c>
       <c r="J70">
-        <v>-5.8601548353099129E-10</v>
+        <v>4.019839029120135E-3</v>
       </c>
       <c r="K70">
-        <v>-5.6153026553183284E-10</v>
+        <v>3.8518799261345439E-3</v>
       </c>
       <c r="L70">
-        <v>-5.380681022425158E-10</v>
+        <v>3.6909385818381379E-3</v>
       </c>
       <c r="M70">
-        <v>-5.1558624783413357E-10</v>
+        <v>3.5367217764164221E-3</v>
       </c>
       <c r="N70">
-        <v>-4.9404374250727677E-10</v>
+        <v>3.3889485415248429E-3</v>
       </c>
       <c r="O70">
-        <v>-4.7340133786717632E-10</v>
+        <v>3.247349648391198E-3</v>
       </c>
       <c r="P70">
-        <v>-4.5362142541686312E-10</v>
+        <v>3.1116671173064322E-3</v>
       </c>
       <c r="Q70">
-        <v>-4.3466796803806409E-10</v>
+        <v>2.9816537476101482E-3</v>
       </c>
       <c r="R70">
-        <v>-4.1650643433500379E-10</v>
+        <v>2.857072667314543E-3</v>
       </c>
       <c r="S70">
-        <v>-3.991037357214861E-10</v>
+        <v>2.7376969015461732E-3</v>
       </c>
       <c r="T70">
-        <v>-3.8242816613663848E-10</v>
+        <v>2.623308959019337E-3</v>
       </c>
       <c r="U70">
-        <v>-3.6644934427948752E-10</v>
+        <v>2.5137004357876531E-3</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>0.94298054941044818</v>
-      </c>
-      <c r="B71" s="1">
-        <v>-8.2451102462884674E-10</v>
+        <v>0.92868110236220525</v>
+      </c>
+      <c r="B71">
+        <v>-1.6967477941566601E-2</v>
       </c>
       <c r="C71">
-        <v>-7.9006085607851494E-10</v>
+        <v>-1.6258533539975209E-2</v>
       </c>
       <c r="D71">
-        <v>-7.5705010322754348E-10</v>
+        <v>-1.557921063936815E-2</v>
       </c>
       <c r="E71">
-        <v>-7.2541862362546647E-10</v>
+        <v>-1.4928271578063351E-2</v>
       </c>
       <c r="F71">
-        <v>-6.9510878772642985E-10</v>
+        <v>-1.430453040703303E-2</v>
       </c>
       <c r="G71">
-        <v>-6.66065373893641E-10</v>
+        <v>-1.370685072921737E-2</v>
       </c>
       <c r="H71">
-        <v>-6.3823546779080277E-10</v>
+        <v>-1.313414362911723E-2</v>
       </c>
       <c r="I71">
-        <v>-6.1156836597722729E-10</v>
+        <v>-1.258536568889377E-2</v>
       </c>
       <c r="J71">
-        <v>-5.8601548353099129E-10</v>
+        <v>-1.2059517087360369E-2</v>
       </c>
       <c r="K71">
-        <v>-5.6153026553183284E-10</v>
+        <v>-1.15556397784036E-2</v>
       </c>
       <c r="L71">
-        <v>-5.380681022425158E-10</v>
+        <v>-1.1072815745514379E-2</v>
       </c>
       <c r="M71">
-        <v>-5.1558624783413357E-10</v>
+        <v>-1.061016532924923E-2</v>
       </c>
       <c r="N71">
-        <v>-4.9404374250727677E-10</v>
+        <v>-1.0166845624574501E-2</v>
       </c>
       <c r="O71">
-        <v>-4.7340133786717632E-10</v>
+        <v>-9.7420489451735641E-3</v>
       </c>
       <c r="P71">
-        <v>-4.5362142541686312E-10</v>
+        <v>-9.3350013519192671E-3</v>
       </c>
       <c r="Q71">
-        <v>-4.3466796803806409E-10</v>
+        <v>-8.9449612428304168E-3</v>
       </c>
       <c r="R71">
-        <v>-4.1650643433500379E-10</v>
+        <v>-8.5712180019436018E-3</v>
       </c>
       <c r="S71">
-        <v>-3.991037357214861E-10</v>
+        <v>-8.2130907046384944E-3</v>
       </c>
       <c r="T71">
-        <v>-3.8242816613663848E-10</v>
+        <v>-7.869926877057988E-3</v>
       </c>
       <c r="U71">
-        <v>-3.6644934427948752E-10</v>
+        <v>-7.5411013073629352E-3</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>0.95499999999999996</v>
-      </c>
-      <c r="B72" s="1">
-        <v>-8.2451102462884674E-10</v>
+        <v>0.93996062992126017</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>-7.9006085607851494E-10</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>-7.5705010322754348E-10</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>-7.2541862362546647E-10</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>-6.9510878772642985E-10</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>-6.66065373893641E-10</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>-6.3823546779080277E-10</v>
+        <v>0</v>
       </c>
       <c r="I72">
-        <v>-6.1156836597722729E-10</v>
+        <v>0</v>
       </c>
       <c r="J72">
-        <v>-5.8601548353099129E-10</v>
+        <v>0</v>
       </c>
       <c r="K72">
-        <v>-5.6153026553183284E-10</v>
+        <v>0</v>
       </c>
       <c r="L72">
-        <v>-5.380681022425158E-10</v>
+        <v>0</v>
       </c>
       <c r="M72">
-        <v>-5.1558624783413357E-10</v>
+        <v>0</v>
       </c>
       <c r="N72">
-        <v>-4.9404374250727677E-10</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>-4.7340133786717632E-10</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>-4.5362142541686312E-10</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>-4.3466796803806409E-10</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>-4.1650643433500379E-10</v>
+        <v>0</v>
       </c>
       <c r="S72">
-        <v>-3.991037357214861E-10</v>
+        <v>0</v>
       </c>
       <c r="T72">
-        <v>-3.8242816613663848E-10</v>
+        <v>0</v>
       </c>
       <c r="U72">
-        <v>-3.6644934427948752E-10</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>0.95500000000000007</v>
+      </c>
+      <c r="B73">
+        <v>5.6558259805222178E-3</v>
+      </c>
+      <c r="C73">
+        <v>5.4195111799917517E-3</v>
+      </c>
+      <c r="D73">
+        <v>5.1930702131227323E-3</v>
+      </c>
+      <c r="E73">
+        <v>4.9760905260211336E-3</v>
+      </c>
+      <c r="F73">
+        <v>4.7681768023443583E-3</v>
+      </c>
+      <c r="G73">
+        <v>4.5689502430724697E-3</v>
+      </c>
+      <c r="H73">
+        <v>4.3780478763724238E-3</v>
+      </c>
+      <c r="I73">
+        <v>4.1951218962979356E-3</v>
+      </c>
+      <c r="J73">
+        <v>4.019839029120135E-3</v>
+      </c>
+      <c r="K73">
+        <v>3.8518799261345439E-3</v>
+      </c>
+      <c r="L73">
+        <v>3.6909385818381379E-3</v>
+      </c>
+      <c r="M73">
+        <v>3.5367217764164221E-3</v>
+      </c>
+      <c r="N73">
+        <v>3.3889485415248429E-3</v>
+      </c>
+      <c r="O73">
+        <v>3.247349648391198E-3</v>
+      </c>
+      <c r="P73">
+        <v>3.1116671173064322E-3</v>
+      </c>
+      <c r="Q73">
+        <v>2.9816537476101482E-3</v>
+      </c>
+      <c r="R73">
+        <v>2.857072667314543E-3</v>
+      </c>
+      <c r="S73">
+        <v>2.7376969015461732E-3</v>
+      </c>
+      <c r="T73">
+        <v>2.623308959019337E-3</v>
+      </c>
+      <c r="U73">
+        <v>2.5137004357876531E-3</v>
       </c>
     </row>
   </sheetData>
